--- a/skills/forestry-survey-summary-tables/assets/report-headers.xlsx
+++ b/skills/forestry-survey-summary-tables/assets/report-headers.xlsx
@@ -8,21 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Finn\Documents\GitHub\agent-skills\skills\forestry-survey-summary-tables\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEA0E98-1DE8-4BDF-9921-3822E416D5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACD0C77-0F80-4225-94BB-E4926C61F13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4610" windowWidth="21600" windowHeight="12670" xr2:uid="{6C185909-5B95-4627-AE85-729272F08AC2}"/>
+    <workbookView xWindow="4520" yWindow="4520" windowWidth="21600" windowHeight="12670" xr2:uid="{6C185909-5B95-4627-AE85-729272F08AC2}"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="2" r:id="rId1"/>
-    <sheet name="2" sheetId="3" r:id="rId2"/>
-    <sheet name="3" sheetId="4" r:id="rId3"/>
-    <sheet name="4" sheetId="5" r:id="rId4"/>
-    <sheet name="5" sheetId="6" r:id="rId5"/>
-    <sheet name="6" sheetId="8" r:id="rId6"/>
-    <sheet name="7" sheetId="7" r:id="rId7"/>
+    <sheet name="B.1" sheetId="2" r:id="rId1"/>
+    <sheet name="B.2" sheetId="3" r:id="rId2"/>
+    <sheet name="B.3" sheetId="4" r:id="rId3"/>
+    <sheet name="B.4" sheetId="5" r:id="rId4"/>
+    <sheet name="B.5" sheetId="9" r:id="rId5"/>
+    <sheet name="B.6" sheetId="6" r:id="rId6"/>
+    <sheet name="B.7" sheetId="8" r:id="rId7"/>
+    <sheet name="小班明细" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'6'!$A$1:$AB$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">B.5!$A$1:$O$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">B.7!$A$1:$AB$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">B.5!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="99">
   <si>
     <t>单位：公顷、立方米</t>
   </si>
@@ -103,10 +106,6 @@
 林地</t>
   </si>
   <si>
-    <t>附表1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>现  状  地  类</t>
   </si>
   <si>
@@ -140,10 +139,6 @@
 迹地</t>
   </si>
   <si>
-    <t>附表2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>森  林  类  别</t>
   </si>
   <si>
@@ -183,10 +178,6 @@
     <t>三级</t>
   </si>
   <si>
-    <t>附表3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>单位：公顷</t>
   </si>
   <si>
@@ -205,10 +196,6 @@
     <t>Ⅳ级</t>
   </si>
   <si>
-    <t>附表4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>重点生态区域名称</t>
   </si>
   <si>
@@ -234,10 +221,6 @@
   </si>
   <si>
     <t>面积</t>
-  </si>
-  <si>
-    <t>附表5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>县</t>
@@ -389,39 +372,76 @@
 性质</t>
   </si>
   <si>
-    <t>附表7</t>
+    <t>单位：公顷、元/平方米、万元</t>
+  </si>
+  <si>
+    <t>总计</t>
+  </si>
+  <si>
+    <t>乔木林地(含迹地)</t>
+  </si>
+  <si>
+    <t>天然林</t>
+  </si>
+  <si>
+    <t>人工林及其它</t>
+  </si>
+  <si>
+    <t>灌木林地</t>
+  </si>
+  <si>
+    <t>其他无立木林地</t>
+  </si>
+  <si>
+    <t>恢复费</t>
+  </si>
+  <si>
+    <t>标准</t>
+  </si>
+  <si>
+    <t>表B.1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>单位：公顷、元/平方米、万元</t>
-  </si>
-  <si>
-    <t>总计</t>
-  </si>
-  <si>
-    <t>乔木林地(含迹地)</t>
-  </si>
-  <si>
-    <t>天然林</t>
-  </si>
-  <si>
-    <t>人工林及其它</t>
-  </si>
-  <si>
-    <t>灌木林地</t>
-  </si>
-  <si>
-    <t>其他无立木林地</t>
-  </si>
-  <si>
-    <t>恢复费</t>
-  </si>
-  <si>
-    <t>标准</t>
-  </si>
-  <si>
-    <t>附表6 使用林地森林植被恢复费测算表</t>
+    <t>表B.2</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>表B.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>表B.4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>表B.6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>表B.7 使用林地森林植被恢复费测算表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>表B.5 项目使用林地分森林类别按地类面积统计表</t>
+  </si>
+  <si>
+    <t>国有</t>
+  </si>
+  <si>
+    <t>集体</t>
+  </si>
+  <si>
+    <t>乔木林地</t>
+  </si>
+  <si>
+    <t>国家特别规定灌木林地</t>
+  </si>
+  <si>
+    <t>一般灌木林地</t>
   </si>
 </sst>
 </file>
@@ -434,7 +454,7 @@
     <numFmt numFmtId="178" formatCode="0_ "/>
     <numFmt numFmtId="179" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,6 +511,21 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -538,7 +573,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -575,40 +610,52 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -942,7 +989,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -985,50 +1032,50 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-      <c r="K3" s="21" t="s">
+      <c r="K3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
     </row>
     <row r="4" spans="1:14" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
     </row>
     <row r="5" spans="1:14" ht="30.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
       <c r="G5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1088,7 +1135,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1140,82 +1187,82 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="21" t="s">
+      <c r="N3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
     </row>
     <row r="4" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
+      <c r="G4" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
     </row>
     <row r="5" spans="1:17" ht="30.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
       <c r="G5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P5" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>15</v>
@@ -1259,7 +1306,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1311,133 +1358,136 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="21" t="s">
+      <c r="N3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
     </row>
     <row r="4" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+    </row>
+    <row r="5" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-    </row>
-    <row r="5" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="16" t="s">
+      <c r="P5" s="18"/>
+      <c r="Q5" s="18"/>
+    </row>
+    <row r="6" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="16" t="s">
+      <c r="I6" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-    </row>
-    <row r="6" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="18" t="s">
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="N6" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="18" t="s">
+      <c r="O6" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="18" t="s">
+      <c r="Q6" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="O6" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="18" t="s">
+    </row>
+    <row r="7" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q6" s="18" t="s">
+      <c r="J7" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="Q6:Q7"/>
     <mergeCell ref="A1:Q2"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="B4:B7"/>
@@ -1454,9 +1504,6 @@
     <mergeCell ref="I6:L6"/>
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:P7"/>
-    <mergeCell ref="Q6:Q7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1480,7 +1527,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1514,61 +1561,61 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
     </row>
     <row r="4" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
+      <c r="G4" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
     </row>
     <row r="5" spans="1:11" ht="30.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
       <c r="G5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1589,6 +1636,214 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A747F49-C3F9-43FD-9F7C-32924351C960}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.58203125" customWidth="1"/>
+    <col min="2" max="2" width="10.58203125" customWidth="1"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1"/>
+    <col min="4" max="15" width="8.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+    </row>
+    <row r="2" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+    </row>
+    <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+    </row>
+    <row r="4" spans="1:15" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="O4" s="26"/>
+    </row>
+    <row r="5" spans="1:15" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="26"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="K5" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="L5" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="M5" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="N5" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="O5" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="27">
+        <v>1</v>
+      </c>
+      <c r="B6" s="26">
+        <v>2</v>
+      </c>
+      <c r="C6" s="26"/>
+      <c r="D6" s="27">
+        <v>3</v>
+      </c>
+      <c r="E6" s="27">
+        <v>4</v>
+      </c>
+      <c r="F6" s="27">
+        <v>5</v>
+      </c>
+      <c r="G6" s="27">
+        <v>6</v>
+      </c>
+      <c r="H6" s="27">
+        <v>7</v>
+      </c>
+      <c r="I6" s="27">
+        <v>8</v>
+      </c>
+      <c r="J6" s="27">
+        <v>9</v>
+      </c>
+      <c r="K6" s="27">
+        <v>10</v>
+      </c>
+      <c r="L6" s="27">
+        <v>11</v>
+      </c>
+      <c r="M6" s="27">
+        <v>12</v>
+      </c>
+      <c r="N6" s="27">
+        <v>13</v>
+      </c>
+      <c r="O6" s="27">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="A1:O2"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="87" fitToHeight="0" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E02BEED-3CB0-4808-9B53-A7ED62920C07}">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -1599,7 +1854,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1622,81 +1877,81 @@
       <c r="G2" s="1"/>
       <c r="H2" s="5"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="13"/>
+      <c r="J2" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="22"/>
     </row>
     <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="13"/>
+      <c r="B4" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="15"/>
+      <c r="E4" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="F4" s="15"/>
+      <c r="G4" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="14" t="s">
+      <c r="H4" s="15"/>
+      <c r="I4" s="23" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15"/>
-      <c r="B4" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="19" t="s">
+      <c r="J4" s="15"/>
+      <c r="K4" s="13"/>
+    </row>
+    <row r="5" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="19" t="s">
+      <c r="D5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" s="17"/>
-      <c r="K4" s="15"/>
-    </row>
-    <row r="5" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="K5" s="15"/>
+        <v>52</v>
+      </c>
+      <c r="K5" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -1716,7 +1971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D53163-EA69-4728-BC12-4022B22CFEA3}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1752,7 +2007,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1832,229 +2087,220 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="7"/>
       <c r="S3" s="5"/>
-      <c r="T3" s="12" t="s">
+      <c r="T3" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
+      <c r="Y3" s="22"/>
+      <c r="Z3" s="22"/>
+      <c r="AA3" s="22"/>
+      <c r="AB3" s="22"/>
+    </row>
+    <row r="4" spans="1:28" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="15"/>
+      <c r="H4" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+    </row>
+    <row r="5" spans="1:28" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="15"/>
+      <c r="Z5" s="15"/>
+      <c r="AA5" s="15"/>
+      <c r="AB5" s="15"/>
+    </row>
+    <row r="6" spans="1:28" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="U6" s="15"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="X6" s="15"/>
+      <c r="Y6" s="15"/>
+      <c r="Z6" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-    </row>
-    <row r="4" spans="1:28" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="16" t="s">
+      <c r="AA6" s="15"/>
+      <c r="AB6" s="15"/>
+    </row>
+    <row r="7" spans="1:28" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G4" s="17"/>
-      <c r="H4" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="17"/>
-      <c r="U4" s="17"/>
-      <c r="V4" s="17"/>
-      <c r="W4" s="17"/>
-      <c r="X4" s="17"/>
-      <c r="Y4" s="17"/>
-      <c r="Z4" s="17"/>
-      <c r="AA4" s="17"/>
-      <c r="AB4" s="17"/>
-    </row>
-    <row r="5" spans="1:28" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="16" t="s">
+      <c r="H7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="17"/>
-      <c r="U5" s="17"/>
-      <c r="V5" s="17"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="17"/>
-      <c r="Y5" s="17"/>
-      <c r="Z5" s="17"/>
-      <c r="AA5" s="17"/>
-      <c r="AB5" s="17"/>
-    </row>
-    <row r="6" spans="1:28" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="16" t="s">
+      <c r="J7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="16" t="s">
+      <c r="M7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="O7" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="17"/>
-      <c r="Z6" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA6" s="17"/>
-      <c r="AB6" s="17"/>
-    </row>
-    <row r="7" spans="1:28" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>91</v>
-      </c>
       <c r="P7" s="6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="S7" s="6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T7" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U7" s="6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="V7" s="6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="W7" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="X7" s="6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="Y7" s="6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Z7" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="AA7" s="6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="AB7" s="6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="H5:J6"/>
-    <mergeCell ref="K5:P5"/>
-    <mergeCell ref="Q5:AB5"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="Q6:S6"/>
-    <mergeCell ref="T6:V6"/>
-    <mergeCell ref="W6:Y6"/>
-    <mergeCell ref="Z6:AB6"/>
     <mergeCell ref="A1:AB2"/>
     <mergeCell ref="T3:AB3"/>
     <mergeCell ref="A4:A7"/>
@@ -2065,6 +2311,15 @@
     <mergeCell ref="F4:G6"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="K4:AB4"/>
+    <mergeCell ref="H5:J6"/>
+    <mergeCell ref="K5:P5"/>
+    <mergeCell ref="Q5:AB5"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="T6:V6"/>
+    <mergeCell ref="W6:Y6"/>
+    <mergeCell ref="Z6:AB6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2072,7 +2327,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82FAAEAC-4E30-4DFF-B50F-4452B5A88A25}">
   <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -2106,7 +2361,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2171,85 +2426,85 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>6</v>
       </c>
       <c r="L3" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="R3" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="M3" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" s="9" t="s">
+      <c r="S3" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="T3" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="U3" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="V3" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="W3" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="X3" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="Y3" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="Z3" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="AA3" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="W3" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="X3" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y3" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z3" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA3" s="9" t="s">
-        <v>81</v>
-      </c>
       <c r="AB3" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/skills/forestry-survey-summary-tables/assets/report-headers.xlsx
+++ b/skills/forestry-survey-summary-tables/assets/report-headers.xlsx
@@ -13,6 +13,7 @@
     <workbookView xWindow="4520" yWindow="4520" windowWidth="21600" windowHeight="12670" xr2:uid="{6C185909-5B95-4627-AE85-729272F08AC2}"/>
   </bookViews>
   <sheets>
+    <sheet name="小班明细" sheetId="7" r:id="rId8"/>
     <sheet name="B.1" sheetId="2" r:id="rId1"/>
     <sheet name="B.2" sheetId="3" r:id="rId2"/>
     <sheet name="B.3" sheetId="4" r:id="rId3"/>
@@ -20,7 +21,6 @@
     <sheet name="B.5" sheetId="9" r:id="rId5"/>
     <sheet name="B.6" sheetId="6" r:id="rId6"/>
     <sheet name="B.7" sheetId="8" r:id="rId7"/>
-    <sheet name="小班明细" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="4">B.5!$A$1:$O$6</definedName>

--- a/skills/forestry-survey-summary-tables/assets/report-headers.xlsx
+++ b/skills/forestry-survey-summary-tables/assets/report-headers.xlsx
@@ -3,10 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15"/>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BD8B19-456B-4CE1-9A6C-1FBD93D14788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BB8B0EE-7174-4770-9C0E-56CF47476E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{CD3EB6B5-00BE-4400-8457-C211054DECAC}"/>
   </bookViews>
@@ -27,7 +24,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">A.1!$A$3:$AB$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">内业处理表!$A$3:$AL$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">外业调查表!$A$3:$AL$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">外业调查表!$A$3:$V$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">原始因子表!$A$3:$AJ$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">A.1!$A$1:$AB$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">B.1!$A$1:$N$35</definedName>
@@ -37,6 +34,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="9">B.5!$A$1:$O$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">B.6!$A$1:$K$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">B.7!$A$1:$M$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">外业调查表!$A$1:$V$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">现状调查表!$A$1:$S$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">A.1!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">B.1!$1:$5</definedName>
@@ -69,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="167">
   <si>
     <t>母表</t>
     <phoneticPr fontId="28" type="noConversion"/>
@@ -1322,158 +1320,158 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="13" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="13" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="181" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="181" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="181" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="181" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2656,97 +2654,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
+      <c r="M1" s="90"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="90"/>
     </row>
     <row r="2" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="92"/>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
+      <c r="A2" s="90"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="90"/>
+      <c r="O2" s="90"/>
     </row>
     <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="91" t="s">
         <v>132</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="91"/>
+      <c r="N3" s="91"/>
+      <c r="O3" s="91"/>
     </row>
     <row r="4" spans="1:15" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="91"/>
-      <c r="D4" s="91" t="s">
+      <c r="C4" s="92"/>
+      <c r="D4" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91" t="s">
+      <c r="E4" s="92"/>
+      <c r="F4" s="92" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91" t="s">
+      <c r="G4" s="92"/>
+      <c r="H4" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91" t="s">
+      <c r="I4" s="92"/>
+      <c r="J4" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91" t="s">
+      <c r="K4" s="92"/>
+      <c r="L4" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="M4" s="91"/>
-      <c r="N4" s="91" t="s">
+      <c r="M4" s="92"/>
+      <c r="N4" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="O4" s="91"/>
+      <c r="O4" s="92"/>
     </row>
     <row r="5" spans="1:15" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="91"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="91"/>
+      <c r="A5" s="92"/>
+      <c r="B5" s="92"/>
+      <c r="C5" s="92"/>
       <c r="D5" s="25" t="s">
         <v>68</v>
       </c>
@@ -2788,10 +2786,10 @@
       <c r="A6" s="27">
         <v>1</v>
       </c>
-      <c r="B6" s="90">
+      <c r="B6" s="93">
         <v>2</v>
       </c>
-      <c r="C6" s="90"/>
+      <c r="C6" s="93"/>
       <c r="D6" s="27">
         <v>3</v>
       </c>
@@ -2830,10 +2828,10 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="91" t="s">
+      <c r="A7" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="92" t="s">
         <v>117</v>
       </c>
       <c r="C7" s="25" t="s">
@@ -2853,8 +2851,8 @@
       <c r="O7" s="26"/>
     </row>
     <row r="8" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="91"/>
-      <c r="B8" s="91"/>
+      <c r="A8" s="92"/>
+      <c r="B8" s="92"/>
       <c r="C8" s="25" t="s">
         <v>133</v>
       </c>
@@ -2872,8 +2870,8 @@
       <c r="O8" s="26"/>
     </row>
     <row r="9" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="91"/>
-      <c r="B9" s="91"/>
+      <c r="A9" s="92"/>
+      <c r="B9" s="92"/>
       <c r="C9" s="25" t="s">
         <v>134</v>
       </c>
@@ -2891,8 +2889,8 @@
       <c r="O9" s="26"/>
     </row>
     <row r="10" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="91"/>
-      <c r="B10" s="91"/>
+      <c r="A10" s="92"/>
+      <c r="B10" s="92"/>
       <c r="C10" s="25" t="s">
         <v>135</v>
       </c>
@@ -2910,8 +2908,8 @@
       <c r="O10" s="26"/>
     </row>
     <row r="11" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="91"/>
-      <c r="B11" s="91" t="s">
+      <c r="A11" s="92"/>
+      <c r="B11" s="92" t="s">
         <v>118</v>
       </c>
       <c r="C11" s="25" t="s">
@@ -2931,8 +2929,8 @@
       <c r="O11" s="26"/>
     </row>
     <row r="12" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="91"/>
-      <c r="B12" s="91"/>
+      <c r="A12" s="92"/>
+      <c r="B12" s="92"/>
       <c r="C12" s="25" t="s">
         <v>136</v>
       </c>
@@ -2950,8 +2948,8 @@
       <c r="O12" s="26"/>
     </row>
     <row r="13" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="91"/>
-      <c r="B13" s="91"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="92"/>
       <c r="C13" s="25" t="s">
         <v>137</v>
       </c>
@@ -2969,8 +2967,8 @@
       <c r="O13" s="26"/>
     </row>
     <row r="14" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="91"/>
-      <c r="B14" s="91" t="s">
+      <c r="A14" s="92"/>
+      <c r="B14" s="92" t="s">
         <v>117</v>
       </c>
       <c r="C14" s="25" t="s">
@@ -2990,8 +2988,8 @@
       <c r="O14" s="26"/>
     </row>
     <row r="15" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="91"/>
-      <c r="B15" s="91"/>
+      <c r="A15" s="92"/>
+      <c r="B15" s="92"/>
       <c r="C15" s="25" t="s">
         <v>133</v>
       </c>
@@ -3009,8 +3007,8 @@
       <c r="O15" s="26"/>
     </row>
     <row r="16" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="91"/>
-      <c r="B16" s="91"/>
+      <c r="A16" s="92"/>
+      <c r="B16" s="92"/>
       <c r="C16" s="25" t="s">
         <v>134</v>
       </c>
@@ -3028,8 +3026,8 @@
       <c r="O16" s="26"/>
     </row>
     <row r="17" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="91"/>
-      <c r="B17" s="91"/>
+      <c r="A17" s="92"/>
+      <c r="B17" s="92"/>
       <c r="C17" s="25" t="s">
         <v>135</v>
       </c>
@@ -3047,8 +3045,8 @@
       <c r="O17" s="26"/>
     </row>
     <row r="18" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="91"/>
-      <c r="B18" s="91" t="s">
+      <c r="A18" s="92"/>
+      <c r="B18" s="92" t="s">
         <v>118</v>
       </c>
       <c r="C18" s="25" t="s">
@@ -3068,8 +3066,8 @@
       <c r="O18" s="26"/>
     </row>
     <row r="19" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="91"/>
-      <c r="B19" s="91"/>
+      <c r="A19" s="92"/>
+      <c r="B19" s="92"/>
       <c r="C19" s="25" t="s">
         <v>136</v>
       </c>
@@ -3087,8 +3085,8 @@
       <c r="O19" s="26"/>
     </row>
     <row r="20" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="91"/>
-      <c r="B20" s="91"/>
+      <c r="A20" s="92"/>
+      <c r="B20" s="92"/>
       <c r="C20" s="25" t="s">
         <v>137</v>
       </c>
@@ -3107,6 +3105,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="A14:A20"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B18:B20"/>
     <mergeCell ref="A1:O2"/>
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A4:A5"/>
@@ -3117,13 +3122,6 @@
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B18:B20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -3145,19 +3143,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="86" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="89" t="s">
@@ -3175,50 +3173,50 @@
       <c r="K2" s="89"/>
     </row>
     <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="87" t="s">
         <v>138</v>
       </c>
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="87" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86" t="s">
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="86"/>
-      <c r="B4" s="86" t="s">
+      <c r="A4" s="87"/>
+      <c r="B4" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="87" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86" t="s">
+      <c r="D4" s="87"/>
+      <c r="E4" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86" t="s">
+      <c r="F4" s="87"/>
+      <c r="G4" s="87" t="s">
         <v>142</v>
       </c>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86" t="s">
+      <c r="H4" s="87"/>
+      <c r="I4" s="87" t="s">
         <v>143</v>
       </c>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
     </row>
     <row r="5" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="86"/>
-      <c r="B5" s="86"/>
+      <c r="A5" s="87"/>
+      <c r="B5" s="87"/>
       <c r="C5" s="16" t="s">
         <v>144</v>
       </c>
@@ -3243,7 +3241,7 @@
       <c r="J5" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="K5" s="86"/>
+      <c r="K5" s="87"/>
     </row>
     <row r="6" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16"/>
@@ -3290,121 +3288,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="86" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="87"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
     </row>
     <row r="2" spans="1:13" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="87"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
     </row>
     <row r="3" spans="1:13" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="95" t="s">
         <v>165</v>
       </c>
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="96"/>
-      <c r="L3" s="96"/>
-      <c r="M3" s="96"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="95"/>
     </row>
     <row r="4" spans="1:13" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="95" t="s">
+      <c r="A4" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="94" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="95" t="s">
+      <c r="C4" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="95" t="s">
+      <c r="D4" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="95" t="s">
+      <c r="E4" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="97" t="s">
+      <c r="F4" s="96" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="98"/>
-      <c r="H4" s="97" t="s">
+      <c r="G4" s="97"/>
+      <c r="H4" s="96" t="s">
         <v>145</v>
       </c>
-      <c r="I4" s="98"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="97" t="s">
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="96" t="s">
         <v>146</v>
       </c>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
+      <c r="L4" s="97"/>
+      <c r="M4" s="97"/>
     </row>
     <row r="5" spans="1:13" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="99"/>
-      <c r="B5" s="99"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="98"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="98"/>
-      <c r="M5" s="98"/>
+      <c r="A5" s="98"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="96"/>
+      <c r="L5" s="97"/>
+      <c r="M5" s="97"/>
     </row>
     <row r="6" spans="1:13" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="99"/>
-      <c r="B6" s="99"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="98"/>
-      <c r="K6" s="98"/>
-      <c r="L6" s="98"/>
-      <c r="M6" s="98"/>
+      <c r="A6" s="98"/>
+      <c r="B6" s="98"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="97"/>
+      <c r="M6" s="97"/>
     </row>
     <row r="7" spans="1:13" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="99"/>
-      <c r="B7" s="99"/>
-      <c r="C7" s="99"/>
-      <c r="D7" s="99"/>
-      <c r="E7" s="99"/>
+      <c r="A7" s="98"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
       <c r="F7" s="19" t="s">
         <v>66</v>
       </c>
@@ -3431,12 +3429,12 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="95"/>
-      <c r="C8" s="95"/>
-      <c r="D8" s="95"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="94"/>
       <c r="E8" s="20" t="s">
         <v>110</v>
       </c>
@@ -3454,10 +3452,10 @@
       <c r="M8" s="21"/>
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="95"/>
-      <c r="B9" s="95"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="95"/>
+      <c r="A9" s="94"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="94"/>
+      <c r="D9" s="94"/>
       <c r="E9" s="20" t="s">
         <v>68</v>
       </c>
@@ -3471,10 +3469,10 @@
       <c r="M9" s="21"/>
     </row>
     <row r="10" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="95"/>
-      <c r="B10" s="95"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="95"/>
+      <c r="A10" s="94"/>
+      <c r="B10" s="94"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="94"/>
       <c r="E10" s="20" t="s">
         <v>69</v>
       </c>
@@ -3488,12 +3486,12 @@
       <c r="M10" s="21"/>
     </row>
     <row r="11" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="95"/>
-      <c r="B11" s="95" t="s">
+      <c r="A11" s="94"/>
+      <c r="B11" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="95"/>
-      <c r="D11" s="95"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
       <c r="E11" s="20" t="s">
         <v>110</v>
       </c>
@@ -3507,10 +3505,10 @@
       <c r="M11" s="21"/>
     </row>
     <row r="12" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="95"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
       <c r="E12" s="20" t="s">
         <v>68</v>
       </c>
@@ -3524,10 +3522,10 @@
       <c r="M12" s="21"/>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="95"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
+      <c r="A13" s="94"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
       <c r="E13" s="20" t="s">
         <v>69</v>
       </c>
@@ -3541,12 +3539,12 @@
       <c r="M13" s="21"/>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="95"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95" t="s">
+      <c r="A14" s="94"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="94" t="s">
         <v>97</v>
       </c>
-      <c r="D14" s="95"/>
+      <c r="D14" s="94"/>
       <c r="E14" s="20" t="s">
         <v>110</v>
       </c>
@@ -3560,10 +3558,10 @@
       <c r="M14" s="21"/>
     </row>
     <row r="15" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="95"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="94"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
       <c r="E15" s="20" t="s">
         <v>68</v>
       </c>
@@ -3577,10 +3575,10 @@
       <c r="M15" s="21"/>
     </row>
     <row r="16" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="95"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="94"/>
+      <c r="C16" s="94"/>
+      <c r="D16" s="94"/>
       <c r="E16" s="20" t="s">
         <v>69</v>
       </c>
@@ -3594,10 +3592,10 @@
       <c r="M16" s="21"/>
     </row>
     <row r="17" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="95"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95" t="s">
+      <c r="A17" s="94"/>
+      <c r="B17" s="94"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="94" t="s">
         <v>110</v>
       </c>
       <c r="E17" s="20" t="s">
@@ -3613,10 +3611,10 @@
       <c r="M17" s="21"/>
     </row>
     <row r="18" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="95"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="94"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
       <c r="E18" s="20" t="s">
         <v>68</v>
       </c>
@@ -3630,10 +3628,10 @@
       <c r="M18" s="21"/>
     </row>
     <row r="19" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="95"/>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
+      <c r="A19" s="94"/>
+      <c r="B19" s="94"/>
+      <c r="C19" s="94"/>
+      <c r="D19" s="94"/>
       <c r="E19" s="20" t="s">
         <v>69</v>
       </c>
@@ -3647,10 +3645,10 @@
       <c r="M19" s="21"/>
     </row>
     <row r="20" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="95"/>
-      <c r="B20" s="95"/>
-      <c r="C20" s="95"/>
-      <c r="D20" s="95"/>
+      <c r="A20" s="94"/>
+      <c r="B20" s="94"/>
+      <c r="C20" s="94"/>
+      <c r="D20" s="94"/>
       <c r="E20" s="20" t="s">
         <v>110</v>
       </c>
@@ -3664,10 +3662,10 @@
       <c r="M20" s="21"/>
     </row>
     <row r="21" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="95"/>
-      <c r="B21" s="95"/>
-      <c r="C21" s="95"/>
-      <c r="D21" s="95"/>
+      <c r="A21" s="94"/>
+      <c r="B21" s="94"/>
+      <c r="C21" s="94"/>
+      <c r="D21" s="94"/>
       <c r="E21" s="20" t="s">
         <v>68</v>
       </c>
@@ -3681,10 +3679,10 @@
       <c r="M21" s="21"/>
     </row>
     <row r="22" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="95"/>
-      <c r="B22" s="95"/>
-      <c r="C22" s="95"/>
-      <c r="D22" s="95"/>
+      <c r="A22" s="94"/>
+      <c r="B22" s="94"/>
+      <c r="C22" s="94"/>
+      <c r="D22" s="94"/>
       <c r="E22" s="20" t="s">
         <v>69</v>
       </c>
@@ -3698,24 +3696,30 @@
       <c r="M22" s="21"/>
     </row>
     <row r="23" spans="1:13" ht="100" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="94" t="s">
+      <c r="A23" s="99" t="s">
         <v>164</v>
       </c>
-      <c r="B23" s="94"/>
-      <c r="C23" s="94"/>
-      <c r="D23" s="94"/>
-      <c r="E23" s="94"/>
-      <c r="F23" s="94"/>
-      <c r="G23" s="94"/>
-      <c r="H23" s="94"/>
-      <c r="I23" s="94"/>
-      <c r="J23" s="94"/>
-      <c r="K23" s="94"/>
-      <c r="L23" s="94"/>
-      <c r="M23" s="94"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="99"/>
+      <c r="G23" s="99"/>
+      <c r="H23" s="99"/>
+      <c r="I23" s="99"/>
+      <c r="J23" s="99"/>
+      <c r="K23" s="99"/>
+      <c r="L23" s="99"/>
+      <c r="M23" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="C14:D16"/>
+    <mergeCell ref="B14:B22"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="C17:C22"/>
+    <mergeCell ref="D20:D22"/>
     <mergeCell ref="B11:D13"/>
     <mergeCell ref="A11:A22"/>
     <mergeCell ref="A1:M2"/>
@@ -3729,12 +3733,6 @@
     <mergeCell ref="D4:D7"/>
     <mergeCell ref="E4:E7"/>
     <mergeCell ref="F4:G6"/>
-    <mergeCell ref="A23:M23"/>
-    <mergeCell ref="C14:D16"/>
-    <mergeCell ref="B14:B22"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="C17:C22"/>
-    <mergeCell ref="D20:D22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -3745,38 +3743,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0129C06E-13CF-437C-A248-525D403143F8}">
-  <dimension ref="A1:XFC19"/>
+  <dimension ref="A1:XEN19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.58203125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="7.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="3.6640625" style="2" customWidth="1"/>
+    <col min="5" max="7" width="6.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.58203125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="3.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="6.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5" style="6" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="3.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="3.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="36" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="15.58203125" style="2" customWidth="1"/>
-    <col min="38" max="16383" width="9" style="1"/>
+    <col min="11" max="11" width="10.58203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.08203125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="4.08203125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="10.4140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.08203125" style="3" customWidth="1"/>
+    <col min="17" max="21" width="4.08203125" style="2" customWidth="1"/>
+    <col min="22" max="22" width="15.58203125" style="2" customWidth="1"/>
+    <col min="23" max="16368" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>150</v>
       </c>
@@ -3786,9 +3774,9 @@
       <c r="E1" s="47"/>
       <c r="F1" s="47"/>
       <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
       <c r="K1" s="47"/>
       <c r="L1" s="47"/>
       <c r="M1" s="47"/>
@@ -3801,23 +3789,8 @@
       <c r="T1" s="47"/>
       <c r="U1" s="47"/>
       <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="47"/>
-      <c r="Z1" s="47"/>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="47"/>
-      <c r="AH1" s="47"/>
-      <c r="AI1" s="47"/>
-      <c r="AJ1" s="47"/>
-      <c r="AK1" s="47"/>
-    </row>
-    <row r="2" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="48" t="s">
         <v>36</v>
       </c>
@@ -3842,23 +3815,8 @@
       <c r="T2" s="48"/>
       <c r="U2" s="48"/>
       <c r="V2" s="48"/>
-      <c r="W2" s="48"/>
-      <c r="X2" s="48"/>
-      <c r="Y2" s="48"/>
-      <c r="Z2" s="48"/>
-      <c r="AA2" s="48"/>
-      <c r="AB2" s="48"/>
-      <c r="AC2" s="48"/>
-      <c r="AD2" s="48"/>
-      <c r="AE2" s="48"/>
-      <c r="AF2" s="48"/>
-      <c r="AG2" s="48"/>
-      <c r="AH2" s="48"/>
-      <c r="AI2" s="48"/>
-      <c r="AJ2" s="48"/>
-      <c r="AK2" s="48"/>
-    </row>
-    <row r="3" spans="1:37" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:22" ht="34.5" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
@@ -3880,98 +3838,53 @@
       <c r="G3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="11" t="s">
+      <c r="J3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="K3" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="P3" s="39" t="s">
+      <c r="M3" s="39" t="s">
         <v>20</v>
       </c>
+      <c r="N3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="Q3" s="8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="U3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="W3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="X3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="AG3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="AH3" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AI3" s="8" t="s">
+      <c r="U3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="AJ3" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AK3" s="8" t="s">
+      <c r="V3" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="10"/>
       <c r="C4" s="9"/>
@@ -3979,38 +3892,23 @@
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
-      <c r="H4" s="41"/>
+      <c r="H4" s="8"/>
       <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="13"/>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="14"/>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="8"/>
-      <c r="AB4" s="8"/>
-      <c r="AC4" s="8"/>
-      <c r="AD4" s="8"/>
-      <c r="AE4" s="15"/>
-      <c r="AF4" s="15"/>
-      <c r="AG4" s="8"/>
-      <c r="AH4" s="8"/>
-      <c r="AI4" s="8"/>
-      <c r="AJ4" s="8"/>
-      <c r="AK4" s="8"/>
-    </row>
-    <row r="5" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M4" s="41"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+    </row>
+    <row r="5" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="10"/>
       <c r="C5" s="9"/>
@@ -4018,38 +3916,23 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
-      <c r="H5" s="41"/>
+      <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
       <c r="L5" s="8"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="43"/>
-      <c r="V5" s="43"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="14"/>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="8"/>
-      <c r="AB5" s="8"/>
-      <c r="AC5" s="8"/>
-      <c r="AD5" s="8"/>
-      <c r="AE5" s="15"/>
-      <c r="AF5" s="15"/>
-      <c r="AG5" s="8"/>
-      <c r="AH5" s="8"/>
-      <c r="AI5" s="8"/>
-      <c r="AJ5" s="8"/>
-      <c r="AK5" s="8"/>
-    </row>
-    <row r="6" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="41"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+    </row>
+    <row r="6" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="10"/>
       <c r="C6" s="9"/>
@@ -4057,38 +3940,23 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
-      <c r="H6" s="41"/>
+      <c r="H6" s="8"/>
       <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
       <c r="L6" s="8"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="43"/>
-      <c r="V6" s="43"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="14"/>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="15"/>
-      <c r="AF6" s="15"/>
-      <c r="AG6" s="8"/>
-      <c r="AH6" s="8"/>
-      <c r="AI6" s="8"/>
-      <c r="AJ6" s="8"/>
-      <c r="AK6" s="8"/>
-    </row>
-    <row r="7" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M6" s="41"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+    </row>
+    <row r="7" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="10"/>
       <c r="C7" s="9"/>
@@ -4096,38 +3964,23 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="41"/>
+      <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
       <c r="L7" s="8"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="43"/>
-      <c r="V7" s="43"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="14"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="8"/>
-      <c r="AD7" s="8"/>
-      <c r="AE7" s="15"/>
-      <c r="AF7" s="15"/>
-      <c r="AG7" s="8"/>
-      <c r="AH7" s="8"/>
-      <c r="AI7" s="8"/>
-      <c r="AJ7" s="8"/>
-      <c r="AK7" s="8"/>
-    </row>
-    <row r="8" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M7" s="41"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+    </row>
+    <row r="8" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="10"/>
       <c r="C8" s="9"/>
@@ -4135,38 +3988,23 @@
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
-      <c r="H8" s="41"/>
+      <c r="H8" s="8"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
       <c r="L8" s="8"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="41"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="43"/>
-      <c r="V8" s="43"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="14"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
-      <c r="AC8" s="8"/>
-      <c r="AD8" s="8"/>
-      <c r="AE8" s="15"/>
-      <c r="AF8" s="15"/>
-      <c r="AG8" s="8"/>
-      <c r="AH8" s="8"/>
-      <c r="AI8" s="8"/>
-      <c r="AJ8" s="8"/>
-      <c r="AK8" s="8"/>
-    </row>
-    <row r="9" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="41"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="15"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+    </row>
+    <row r="9" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
       <c r="B9" s="10"/>
       <c r="C9" s="9"/>
@@ -4174,38 +4012,23 @@
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="41"/>
+      <c r="H9" s="8"/>
       <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
       <c r="L9" s="8"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="43"/>
-      <c r="W9" s="13"/>
-      <c r="X9" s="12"/>
-      <c r="Y9" s="14"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="8"/>
-      <c r="AB9" s="8"/>
-      <c r="AC9" s="8"/>
-      <c r="AD9" s="8"/>
-      <c r="AE9" s="15"/>
-      <c r="AF9" s="15"/>
-      <c r="AG9" s="8"/>
-      <c r="AH9" s="8"/>
-      <c r="AI9" s="8"/>
-      <c r="AJ9" s="8"/>
-      <c r="AK9" s="8"/>
-    </row>
-    <row r="10" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M9" s="41"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+    </row>
+    <row r="10" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="B10" s="10"/>
       <c r="C10" s="9"/>
@@ -4213,38 +4036,23 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="41"/>
+      <c r="H10" s="8"/>
       <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
       <c r="L10" s="8"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="13"/>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="14"/>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="8"/>
-      <c r="AB10" s="8"/>
-      <c r="AC10" s="8"/>
-      <c r="AD10" s="8"/>
-      <c r="AE10" s="15"/>
-      <c r="AF10" s="15"/>
-      <c r="AG10" s="8"/>
-      <c r="AH10" s="8"/>
-      <c r="AI10" s="8"/>
-      <c r="AJ10" s="8"/>
-      <c r="AK10" s="8"/>
-    </row>
-    <row r="11" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M10" s="41"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+    </row>
+    <row r="11" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
       <c r="B11" s="10"/>
       <c r="C11" s="9"/>
@@ -4252,38 +4060,23 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="41"/>
+      <c r="H11" s="8"/>
       <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
       <c r="L11" s="8"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="41"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="43"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="12"/>
-      <c r="Y11" s="14"/>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="8"/>
-      <c r="AE11" s="15"/>
-      <c r="AF11" s="15"/>
-      <c r="AG11" s="8"/>
-      <c r="AH11" s="8"/>
-      <c r="AI11" s="8"/>
-      <c r="AJ11" s="8"/>
-      <c r="AK11" s="8"/>
-    </row>
-    <row r="12" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M11" s="41"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="15"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+    </row>
+    <row r="12" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="10"/>
       <c r="C12" s="9"/>
@@ -4291,38 +4084,23 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="41"/>
+      <c r="H12" s="8"/>
       <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
       <c r="L12" s="8"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="41"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="43"/>
-      <c r="W12" s="13"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="14"/>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="8"/>
-      <c r="AB12" s="8"/>
-      <c r="AC12" s="8"/>
-      <c r="AD12" s="8"/>
-      <c r="AE12" s="15"/>
-      <c r="AF12" s="15"/>
-      <c r="AG12" s="8"/>
-      <c r="AH12" s="8"/>
-      <c r="AI12" s="8"/>
-      <c r="AJ12" s="8"/>
-      <c r="AK12" s="8"/>
-    </row>
-    <row r="13" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M12" s="41"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+    </row>
+    <row r="13" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="10"/>
       <c r="C13" s="9"/>
@@ -4330,38 +4108,23 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="41"/>
+      <c r="H13" s="8"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
       <c r="L13" s="8"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="43"/>
-      <c r="W13" s="13"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="14"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="15"/>
-      <c r="AF13" s="15"/>
-      <c r="AG13" s="8"/>
-      <c r="AH13" s="8"/>
-      <c r="AI13" s="8"/>
-      <c r="AJ13" s="8"/>
-      <c r="AK13" s="8"/>
-    </row>
-    <row r="14" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M13" s="41"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="15"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+    </row>
+    <row r="14" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="10"/>
       <c r="C14" s="9"/>
@@ -4369,38 +4132,23 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
-      <c r="H14" s="41"/>
+      <c r="H14" s="8"/>
       <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
       <c r="L14" s="8"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="43"/>
-      <c r="W14" s="13"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="14"/>
-      <c r="Z14" s="14"/>
-      <c r="AA14" s="8"/>
-      <c r="AB14" s="8"/>
-      <c r="AC14" s="8"/>
-      <c r="AD14" s="8"/>
-      <c r="AE14" s="15"/>
-      <c r="AF14" s="15"/>
-      <c r="AG14" s="8"/>
-      <c r="AH14" s="8"/>
-      <c r="AI14" s="8"/>
-      <c r="AJ14" s="8"/>
-      <c r="AK14" s="8"/>
-    </row>
-    <row r="15" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M14" s="41"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="15"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+    </row>
+    <row r="15" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="10"/>
       <c r="C15" s="9"/>
@@ -4408,38 +4156,23 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
-      <c r="H15" s="41"/>
+      <c r="H15" s="8"/>
       <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
       <c r="L15" s="8"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="12"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="43"/>
-      <c r="W15" s="13"/>
-      <c r="X15" s="12"/>
-      <c r="Y15" s="14"/>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="8"/>
-      <c r="AB15" s="8"/>
-      <c r="AC15" s="8"/>
-      <c r="AD15" s="8"/>
-      <c r="AE15" s="15"/>
-      <c r="AF15" s="15"/>
-      <c r="AG15" s="8"/>
-      <c r="AH15" s="8"/>
-      <c r="AI15" s="8"/>
-      <c r="AJ15" s="8"/>
-      <c r="AK15" s="8"/>
-    </row>
-    <row r="16" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M15" s="41"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
+      <c r="V15" s="8"/>
+    </row>
+    <row r="16" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="10"/>
       <c r="C16" s="9"/>
@@ -4447,38 +4180,23 @@
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
-      <c r="H16" s="41"/>
+      <c r="H16" s="8"/>
       <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
       <c r="L16" s="8"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="12"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="43"/>
-      <c r="W16" s="13"/>
-      <c r="X16" s="12"/>
-      <c r="Y16" s="14"/>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="8"/>
-      <c r="AB16" s="8"/>
-      <c r="AC16" s="8"/>
-      <c r="AD16" s="8"/>
-      <c r="AE16" s="15"/>
-      <c r="AF16" s="15"/>
-      <c r="AG16" s="8"/>
-      <c r="AH16" s="8"/>
-      <c r="AI16" s="8"/>
-      <c r="AJ16" s="8"/>
-      <c r="AK16" s="8"/>
-    </row>
-    <row r="17" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M16" s="41"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="15"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+    </row>
+    <row r="17" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="10"/>
       <c r="C17" s="9"/>
@@ -4486,38 +4204,23 @@
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="41"/>
+      <c r="H17" s="8"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
       <c r="L17" s="8"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="43"/>
-      <c r="V17" s="43"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="14"/>
-      <c r="Z17" s="14"/>
-      <c r="AA17" s="8"/>
-      <c r="AB17" s="8"/>
-      <c r="AC17" s="8"/>
-      <c r="AD17" s="8"/>
-      <c r="AE17" s="15"/>
-      <c r="AF17" s="15"/>
-      <c r="AG17" s="8"/>
-      <c r="AH17" s="8"/>
-      <c r="AI17" s="8"/>
-      <c r="AJ17" s="8"/>
-      <c r="AK17" s="8"/>
-    </row>
-    <row r="18" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M17" s="41"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+    </row>
+    <row r="18" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="10"/>
       <c r="C18" s="9"/>
@@ -4525,38 +4228,23 @@
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="41"/>
+      <c r="H18" s="8"/>
       <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
       <c r="L18" s="8"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="41"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="43"/>
-      <c r="V18" s="43"/>
-      <c r="W18" s="13"/>
-      <c r="X18" s="12"/>
-      <c r="Y18" s="14"/>
-      <c r="Z18" s="14"/>
-      <c r="AA18" s="8"/>
-      <c r="AB18" s="8"/>
-      <c r="AC18" s="8"/>
-      <c r="AD18" s="8"/>
-      <c r="AE18" s="15"/>
-      <c r="AF18" s="15"/>
-      <c r="AG18" s="8"/>
-      <c r="AH18" s="8"/>
-      <c r="AI18" s="8"/>
-      <c r="AJ18" s="8"/>
-      <c r="AK18" s="8"/>
-    </row>
-    <row r="19" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M18" s="41"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="15"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+    </row>
+    <row r="19" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="10"/>
       <c r="C19" s="9"/>
@@ -4564,48 +4252,33 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-      <c r="H19" s="41"/>
+      <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
       <c r="L19" s="8"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="41"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="12"/>
-      <c r="T19" s="12"/>
-      <c r="U19" s="43"/>
-      <c r="V19" s="43"/>
-      <c r="W19" s="13"/>
-      <c r="X19" s="12"/>
-      <c r="Y19" s="14"/>
-      <c r="Z19" s="14"/>
-      <c r="AA19" s="8"/>
-      <c r="AB19" s="8"/>
-      <c r="AC19" s="8"/>
-      <c r="AD19" s="8"/>
-      <c r="AE19" s="15"/>
-      <c r="AF19" s="15"/>
-      <c r="AG19" s="8"/>
-      <c r="AH19" s="8"/>
-      <c r="AI19" s="8"/>
-      <c r="AJ19" s="8"/>
-      <c r="AK19" s="8"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="15"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="A2:AK2"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:V2"/>
   </mergeCells>
   <phoneticPr fontId="28" type="noConversion"/>
-  <dataValidations count="10">
+  <dataValidations count="8">
     <dataValidation type="list" sqref="E4:E1048576" xr:uid="{974784D5-B160-4102-A1D8-2EBE98ADA91F}">
       <formula1>"防护林林地,特用林林地,用材林林地,经济林林地,能源林林地,薪炭林林地,苗圃地"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请输入整数年数" error="林龄须为不小于0的整数，或留空。" promptTitle="林龄（年）" prompt="填写非负整数年数；未知或不适用时留空。" sqref="P4:P1048576" xr:uid="{A3A4BA28-8344-4328-94D1-3EAF74F534F7}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请输入整数年数" error="林龄须为不小于0的整数，或留空。" promptTitle="林龄（年）" prompt="填写非负整数年数；未知或不适用时留空。" sqref="M4:M1048576" xr:uid="{A3A4BA28-8344-4328-94D1-3EAF74F534F7}">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G1048576" xr:uid="{2D2A3B2D-4ED9-4D29-9763-8FC7B1994552}">
@@ -4617,19 +4290,13 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F1048576" xr:uid="{1588E7FD-AB22-46EF-BE18-0CB76772C539}">
       <formula1>"国有,集体"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H1048576" xr:uid="{05BC35EB-626B-4579-99B4-8D3166AFA4B8}">
-      <formula1>"国家公益林,地方公益林"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I1048576" xr:uid="{9F92F464-06ED-4F97-8160-DD240555DF67}">
-      <formula1>"Ⅰ,Ⅱ,Ⅲ,Ⅳ"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K1048576" xr:uid="{760749ED-14F1-4C45-92F1-AEB68B080270}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I1048576" xr:uid="{760749ED-14F1-4C45-92F1-AEB68B080270}">
       <formula1>"人工,天然"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O4:O1048576" xr:uid="{1B78DBF0-3267-4FDF-9BBF-576AF353D20E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L1048576" xr:uid="{1B78DBF0-3267-4FDF-9BBF-576AF353D20E}">
       <formula1>"幼龄林,中龄林,近熟林,成熟林,过熟林,产前期,初产期,盛产期,衰退期,幼龄竹,壮龄竹,老龄竹"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J1048576" xr:uid="{010052FE-0037-4F17-A1E0-723B0B763FB7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H1048576" xr:uid="{010052FE-0037-4F17-A1E0-723B0B763FB7}">
       <formula1>"水源涵养林,水土保持林,防风固沙林,农田牧场防护林,护岸林,护路林,其他防护林,国防林,实验林,母树林,环境保护林,风景林,名胜古迹和革命纪念林,自然保护林,短轮伐期工业原料用材林,速生丰产用材林,一般用材林,薪炭林,果树林,食用原料林,林化工业原料林,药用林,其他经济林,水源林,水保林,用材林,能源林"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5549,27 +5216,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="72" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="28"/>
@@ -5587,98 +5254,98 @@
       <c r="M2" s="28"/>
       <c r="N2" s="28"/>
       <c r="O2" s="28"/>
-      <c r="P2" s="51" t="s">
+      <c r="P2" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
     </row>
     <row r="3" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="53" t="s">
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="53"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="53"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="53"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="58"/>
+      <c r="P3" s="58"/>
+      <c r="Q3" s="58"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="58"/>
     </row>
     <row r="4" spans="1:19" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53" t="s">
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="53"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="53" t="s">
+      <c r="L4" s="58"/>
+      <c r="M4" s="84"/>
+      <c r="N4" s="84"/>
+      <c r="O4" s="84"/>
+      <c r="P4" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="Q4" s="53"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="53"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="82"/>
+      <c r="S4" s="58"/>
     </row>
     <row r="5" spans="1:19" ht="26.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="76" t="s">
+      <c r="B5" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="76"/>
-      <c r="D5" s="53" t="s">
+      <c r="C5" s="59"/>
+      <c r="D5" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53" t="s">
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53"/>
-      <c r="N5" s="53"/>
-      <c r="O5" s="53"/>
-      <c r="P5" s="53"/>
-      <c r="Q5" s="53"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="53"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="58"/>
+      <c r="N5" s="58"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="58"/>
+      <c r="Q5" s="58"/>
+      <c r="R5" s="58"/>
+      <c r="S5" s="58"/>
     </row>
     <row r="6" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="75"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="77"/>
+      <c r="A6" s="57"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="60"/>
       <c r="D6" s="38" t="s">
         <v>51</v>
       </c>
@@ -5729,8 +5396,8 @@
       </c>
     </row>
     <row r="7" spans="1:19" ht="26.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="75"/>
-      <c r="B7" s="53" t="s">
+      <c r="A7" s="57"/>
+      <c r="B7" s="58" t="s">
         <v>66</v>
       </c>
       <c r="C7" s="37" t="s">
@@ -5754,8 +5421,8 @@
       <c r="S7" s="29"/>
     </row>
     <row r="8" spans="1:19" ht="26.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="75"/>
-      <c r="B8" s="53"/>
+      <c r="A8" s="57"/>
+      <c r="B8" s="58"/>
       <c r="C8" s="37" t="s">
         <v>68</v>
       </c>
@@ -5777,8 +5444,8 @@
       <c r="S8" s="31"/>
     </row>
     <row r="9" spans="1:19" ht="26.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="75"/>
-      <c r="B9" s="53"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="58"/>
       <c r="C9" s="37" t="s">
         <v>69</v>
       </c>
@@ -5800,8 +5467,8 @@
       <c r="S9" s="29"/>
     </row>
     <row r="10" spans="1:19" ht="26.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="75"/>
-      <c r="B10" s="53" t="s">
+      <c r="A10" s="57"/>
+      <c r="B10" s="58" t="s">
         <v>70</v>
       </c>
       <c r="C10" s="37" t="s">
@@ -5825,8 +5492,8 @@
       <c r="S10" s="34"/>
     </row>
     <row r="11" spans="1:19" ht="26.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="75"/>
-      <c r="B11" s="53"/>
+      <c r="A11" s="57"/>
+      <c r="B11" s="58"/>
       <c r="C11" s="37" t="s">
         <v>68</v>
       </c>
@@ -5848,8 +5515,8 @@
       <c r="S11" s="34"/>
     </row>
     <row r="12" spans="1:19" ht="26.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="75"/>
-      <c r="B12" s="53"/>
+      <c r="A12" s="57"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="37" t="s">
         <v>69</v>
       </c>
@@ -5871,92 +5538,92 @@
       <c r="S12" s="34"/>
     </row>
     <row r="13" spans="1:19" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="56"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="53"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="53"/>
-      <c r="P13" s="53"/>
-      <c r="Q13" s="53"/>
-      <c r="R13" s="53"/>
-      <c r="S13" s="53"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="58"/>
+      <c r="L13" s="58"/>
+      <c r="M13" s="58"/>
+      <c r="N13" s="58"/>
+      <c r="O13" s="58"/>
+      <c r="P13" s="58"/>
+      <c r="Q13" s="58"/>
+      <c r="R13" s="58"/>
+      <c r="S13" s="58"/>
     </row>
     <row r="14" spans="1:19" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="57"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="54"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="54"/>
-      <c r="N14" s="54"/>
-      <c r="O14" s="54"/>
-      <c r="P14" s="54"/>
-      <c r="Q14" s="54"/>
-      <c r="R14" s="54"/>
-      <c r="S14" s="54"/>
+      <c r="A14" s="83"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="84"/>
+      <c r="N14" s="84"/>
+      <c r="O14" s="84"/>
+      <c r="P14" s="84"/>
+      <c r="Q14" s="84"/>
+      <c r="R14" s="84"/>
+      <c r="S14" s="84"/>
     </row>
     <row r="15" spans="1:19" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="59"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="53"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="53"/>
-      <c r="P15" s="53"/>
-      <c r="Q15" s="53"/>
-      <c r="R15" s="53"/>
-      <c r="S15" s="53"/>
+      <c r="A15" s="71"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="58"/>
+      <c r="L15" s="58"/>
+      <c r="M15" s="58"/>
+      <c r="N15" s="58"/>
+      <c r="O15" s="58"/>
+      <c r="P15" s="58"/>
+      <c r="Q15" s="58"/>
+      <c r="R15" s="58"/>
+      <c r="S15" s="58"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="49" t="s">
+      <c r="A16" s="72" t="s">
         <v>153</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60"/>
-      <c r="M16" s="60"/>
-      <c r="N16" s="60"/>
-      <c r="O16" s="60"/>
-      <c r="P16" s="60"/>
-      <c r="Q16" s="60"/>
-      <c r="R16" s="60"/>
-      <c r="S16" s="60"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="73"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="73"/>
+      <c r="O16" s="73"/>
+      <c r="P16" s="73"/>
+      <c r="Q16" s="73"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="73"/>
     </row>
     <row r="17" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="28"/>
@@ -5974,413 +5641,436 @@
       <c r="M17" s="28"/>
       <c r="N17" s="28"/>
       <c r="O17" s="28"/>
-      <c r="P17" s="51" t="s">
+      <c r="P17" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="Q17" s="52"/>
-      <c r="R17" s="52"/>
-      <c r="S17" s="52"/>
+      <c r="Q17" s="81"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="81"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="61" t="s">
+      <c r="A18" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="62"/>
-      <c r="M18" s="62"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="62"/>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="62"/>
-      <c r="R18" s="62"/>
-      <c r="S18" s="63"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="75"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="75"/>
+      <c r="J18" s="75"/>
+      <c r="K18" s="75"/>
+      <c r="L18" s="75"/>
+      <c r="M18" s="75"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="75"/>
+      <c r="P18" s="75"/>
+      <c r="Q18" s="75"/>
+      <c r="R18" s="75"/>
+      <c r="S18" s="76"/>
     </row>
     <row r="19" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="58" t="s">
+      <c r="A19" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="58"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="58"/>
-      <c r="O19" s="58"/>
-      <c r="P19" s="58"/>
-      <c r="Q19" s="58"/>
-      <c r="R19" s="58"/>
-      <c r="S19" s="58"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="65"/>
+      <c r="P19" s="65"/>
+      <c r="Q19" s="65"/>
+      <c r="R19" s="65"/>
+      <c r="S19" s="65"/>
     </row>
     <row r="20" spans="1:19" ht="35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="64"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="65"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="65"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="65"/>
-      <c r="M20" s="65"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="65"/>
-      <c r="P20" s="65"/>
-      <c r="Q20" s="65"/>
-      <c r="R20" s="65"/>
-      <c r="S20" s="66"/>
+      <c r="A20" s="77"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="78"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="78"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="78"/>
+      <c r="L20" s="78"/>
+      <c r="M20" s="78"/>
+      <c r="N20" s="78"/>
+      <c r="O20" s="78"/>
+      <c r="P20" s="78"/>
+      <c r="Q20" s="78"/>
+      <c r="R20" s="78"/>
+      <c r="S20" s="79"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="58" t="s">
+      <c r="A21" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="58"/>
-      <c r="O21" s="58"/>
-      <c r="P21" s="58"/>
-      <c r="Q21" s="58"/>
-      <c r="R21" s="58"/>
-      <c r="S21" s="58"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="65"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="65"/>
+      <c r="S21" s="65"/>
     </row>
     <row r="22" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="81"/>
-      <c r="B22" s="82"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="82"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="82"/>
-      <c r="H22" s="82"/>
-      <c r="I22" s="82"/>
-      <c r="J22" s="82"/>
-      <c r="K22" s="82"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="82"/>
-      <c r="N22" s="82"/>
-      <c r="O22" s="82"/>
-      <c r="P22" s="82"/>
-      <c r="Q22" s="82"/>
-      <c r="R22" s="82"/>
-      <c r="S22" s="83"/>
+      <c r="A22" s="66"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="67"/>
+      <c r="P22" s="67"/>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="68"/>
     </row>
     <row r="23" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="58" t="s">
+      <c r="A23" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="58"/>
-      <c r="O23" s="58"/>
-      <c r="P23" s="58"/>
-      <c r="Q23" s="58"/>
-      <c r="R23" s="58"/>
-      <c r="S23" s="58"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="65"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="65"/>
+      <c r="P23" s="65"/>
+      <c r="Q23" s="65"/>
+      <c r="R23" s="65"/>
+      <c r="S23" s="65"/>
     </row>
     <row r="24" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="67"/>
-      <c r="B24" s="84"/>
-      <c r="C24" s="84"/>
-      <c r="D24" s="84"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="84"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="84"/>
-      <c r="J24" s="84"/>
-      <c r="K24" s="84"/>
-      <c r="L24" s="84"/>
-      <c r="M24" s="84"/>
-      <c r="N24" s="84"/>
-      <c r="O24" s="84"/>
-      <c r="P24" s="84"/>
-      <c r="Q24" s="84"/>
-      <c r="R24" s="84"/>
-      <c r="S24" s="85"/>
+      <c r="A24" s="49"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="69"/>
+      <c r="K24" s="69"/>
+      <c r="L24" s="69"/>
+      <c r="M24" s="69"/>
+      <c r="N24" s="69"/>
+      <c r="O24" s="69"/>
+      <c r="P24" s="69"/>
+      <c r="Q24" s="69"/>
+      <c r="R24" s="69"/>
+      <c r="S24" s="70"/>
     </row>
     <row r="25" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="58" t="s">
+      <c r="A25" s="65" t="s">
         <v>154</v>
       </c>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
-      <c r="P25" s="58"/>
-      <c r="Q25" s="58"/>
-      <c r="R25" s="58"/>
-      <c r="S25" s="58"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="65"/>
+      <c r="P25" s="65"/>
+      <c r="Q25" s="65"/>
+      <c r="R25" s="65"/>
+      <c r="S25" s="65"/>
     </row>
     <row r="26" spans="1:19" ht="35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="76"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="56"/>
-      <c r="K26" s="56"/>
-      <c r="L26" s="56"/>
-      <c r="M26" s="56"/>
-      <c r="N26" s="56"/>
-      <c r="O26" s="56"/>
-      <c r="P26" s="56"/>
-      <c r="Q26" s="56"/>
-      <c r="R26" s="56"/>
-      <c r="S26" s="56"/>
+      <c r="A26" s="59"/>
+      <c r="B26" s="61"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="61"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="61"/>
+      <c r="O26" s="61"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="61"/>
+      <c r="R26" s="61"/>
+      <c r="S26" s="61"/>
     </row>
     <row r="27" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="78" t="s">
+      <c r="A27" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="79"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="79"/>
-      <c r="F27" s="79"/>
-      <c r="G27" s="79"/>
-      <c r="H27" s="79"/>
-      <c r="I27" s="79"/>
-      <c r="J27" s="79"/>
-      <c r="K27" s="79"/>
-      <c r="L27" s="79"/>
-      <c r="M27" s="79"/>
-      <c r="N27" s="79"/>
-      <c r="O27" s="79"/>
-      <c r="P27" s="79"/>
-      <c r="Q27" s="79"/>
-      <c r="R27" s="79"/>
-      <c r="S27" s="79"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="63"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="63"/>
+      <c r="L27" s="63"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="63"/>
+      <c r="P27" s="63"/>
+      <c r="Q27" s="63"/>
+      <c r="R27" s="63"/>
+      <c r="S27" s="63"/>
     </row>
     <row r="28" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="80"/>
-      <c r="B28" s="80"/>
-      <c r="C28" s="80"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="80"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="80"/>
-      <c r="I28" s="80"/>
-      <c r="J28" s="80"/>
-      <c r="K28" s="80"/>
-      <c r="L28" s="80"/>
-      <c r="M28" s="80"/>
-      <c r="N28" s="80"/>
-      <c r="O28" s="80"/>
-      <c r="P28" s="80"/>
-      <c r="Q28" s="80"/>
-      <c r="R28" s="80"/>
-      <c r="S28" s="80"/>
+      <c r="A28" s="64"/>
+      <c r="B28" s="64"/>
+      <c r="C28" s="64"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="64"/>
+      <c r="M28" s="64"/>
+      <c r="N28" s="64"/>
+      <c r="O28" s="64"/>
+      <c r="P28" s="64"/>
+      <c r="Q28" s="64"/>
+      <c r="R28" s="64"/>
+      <c r="S28" s="64"/>
     </row>
     <row r="29" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="58" t="s">
+      <c r="A29" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="58"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="58"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
-      <c r="P29" s="58"/>
-      <c r="Q29" s="58"/>
-      <c r="R29" s="58"/>
-      <c r="S29" s="58"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="65"/>
+      <c r="M29" s="65"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="65"/>
+      <c r="P29" s="65"/>
+      <c r="Q29" s="65"/>
+      <c r="R29" s="65"/>
+      <c r="S29" s="65"/>
     </row>
     <row r="30" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="77"/>
-      <c r="B30" s="77"/>
-      <c r="C30" s="77"/>
-      <c r="D30" s="77"/>
-      <c r="E30" s="77"/>
-      <c r="F30" s="77"/>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
-      <c r="I30" s="77"/>
-      <c r="J30" s="77"/>
-      <c r="K30" s="77"/>
-      <c r="L30" s="77"/>
-      <c r="M30" s="77"/>
-      <c r="N30" s="77"/>
-      <c r="O30" s="77"/>
-      <c r="P30" s="77"/>
-      <c r="Q30" s="77"/>
-      <c r="R30" s="77"/>
-      <c r="S30" s="77"/>
+      <c r="A30" s="60"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="60"/>
+      <c r="K30" s="60"/>
+      <c r="L30" s="60"/>
+      <c r="M30" s="60"/>
+      <c r="N30" s="60"/>
+      <c r="O30" s="60"/>
+      <c r="P30" s="60"/>
+      <c r="Q30" s="60"/>
+      <c r="R30" s="60"/>
+      <c r="S30" s="60"/>
     </row>
     <row r="31" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="77"/>
-      <c r="B31" s="77"/>
-      <c r="C31" s="77"/>
-      <c r="D31" s="77"/>
-      <c r="E31" s="77"/>
-      <c r="F31" s="77"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="77"/>
-      <c r="J31" s="77"/>
-      <c r="K31" s="77"/>
-      <c r="L31" s="77"/>
-      <c r="M31" s="77"/>
-      <c r="N31" s="77"/>
-      <c r="O31" s="77"/>
-      <c r="P31" s="77"/>
-      <c r="Q31" s="77"/>
-      <c r="R31" s="77"/>
-      <c r="S31" s="77"/>
+      <c r="A31" s="60"/>
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="60"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="60"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="60"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="60"/>
     </row>
     <row r="32" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="77"/>
-      <c r="B32" s="77"/>
-      <c r="C32" s="77"/>
-      <c r="D32" s="77"/>
-      <c r="E32" s="77"/>
-      <c r="F32" s="77"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-      <c r="I32" s="77"/>
-      <c r="J32" s="77"/>
-      <c r="K32" s="77"/>
-      <c r="L32" s="77"/>
-      <c r="M32" s="77"/>
-      <c r="N32" s="77"/>
-      <c r="O32" s="77"/>
-      <c r="P32" s="77"/>
-      <c r="Q32" s="77"/>
-      <c r="R32" s="77"/>
-      <c r="S32" s="77"/>
+      <c r="A32" s="60"/>
+      <c r="B32" s="60"/>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="60"/>
+      <c r="K32" s="60"/>
+      <c r="L32" s="60"/>
+      <c r="M32" s="60"/>
+      <c r="N32" s="60"/>
+      <c r="O32" s="60"/>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="60"/>
+      <c r="R32" s="60"/>
+      <c r="S32" s="60"/>
     </row>
     <row r="33" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="58" t="s">
+      <c r="A33" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="58"/>
-      <c r="C33" s="58"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="58"/>
-      <c r="K33" s="58"/>
-      <c r="L33" s="58"/>
-      <c r="M33" s="58"/>
-      <c r="N33" s="58"/>
-      <c r="O33" s="58"/>
-      <c r="P33" s="58"/>
-      <c r="Q33" s="58"/>
-      <c r="R33" s="58"/>
-      <c r="S33" s="58"/>
+      <c r="B33" s="65"/>
+      <c r="C33" s="65"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="65"/>
+      <c r="H33" s="65"/>
+      <c r="I33" s="65"/>
+      <c r="J33" s="65"/>
+      <c r="K33" s="65"/>
+      <c r="L33" s="65"/>
+      <c r="M33" s="65"/>
+      <c r="N33" s="65"/>
+      <c r="O33" s="65"/>
+      <c r="P33" s="65"/>
+      <c r="Q33" s="65"/>
+      <c r="R33" s="65"/>
+      <c r="S33" s="65"/>
     </row>
     <row r="34" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="67" t="s">
+      <c r="A34" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="B34" s="68"/>
-      <c r="C34" s="68"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="69"/>
-      <c r="I34" s="69"/>
-      <c r="J34" s="69"/>
-      <c r="K34" s="69"/>
-      <c r="L34" s="69"/>
-      <c r="M34" s="69"/>
-      <c r="N34" s="69"/>
-      <c r="O34" s="69"/>
-      <c r="P34" s="69"/>
-      <c r="Q34" s="69"/>
-      <c r="R34" s="69"/>
-      <c r="S34" s="70"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="51"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="51"/>
+      <c r="K34" s="51"/>
+      <c r="L34" s="51"/>
+      <c r="M34" s="51"/>
+      <c r="N34" s="51"/>
+      <c r="O34" s="51"/>
+      <c r="P34" s="51"/>
+      <c r="Q34" s="51"/>
+      <c r="R34" s="51"/>
+      <c r="S34" s="52"/>
     </row>
     <row r="35" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="71" t="s">
+      <c r="A35" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
-      <c r="G35" s="73"/>
-      <c r="H35" s="73"/>
-      <c r="I35" s="73"/>
-      <c r="J35" s="73"/>
-      <c r="K35" s="73"/>
-      <c r="L35" s="73"/>
-      <c r="M35" s="73"/>
-      <c r="N35" s="73"/>
-      <c r="O35" s="73"/>
-      <c r="P35" s="73"/>
-      <c r="Q35" s="73"/>
-      <c r="R35" s="73"/>
-      <c r="S35" s="74"/>
+      <c r="B35" s="54"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="55"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="55"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="55"/>
+      <c r="J35" s="55"/>
+      <c r="K35" s="55"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="55"/>
+      <c r="N35" s="55"/>
+      <c r="O35" s="55"/>
+      <c r="P35" s="55"/>
+      <c r="Q35" s="55"/>
+      <c r="R35" s="55"/>
+      <c r="S35" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:S3"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="K5:S5"/>
+    <mergeCell ref="A13:S13"/>
+    <mergeCell ref="A14:S14"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="A25:S25"/>
+    <mergeCell ref="A15:S15"/>
+    <mergeCell ref="A16:S16"/>
+    <mergeCell ref="A18:S18"/>
+    <mergeCell ref="A19:S19"/>
+    <mergeCell ref="A20:S20"/>
+    <mergeCell ref="P17:S17"/>
     <mergeCell ref="A34:S34"/>
     <mergeCell ref="A35:S35"/>
     <mergeCell ref="A5:A12"/>
@@ -6397,29 +6087,6 @@
     <mergeCell ref="A22:S22"/>
     <mergeCell ref="A23:S23"/>
     <mergeCell ref="A24:S24"/>
-    <mergeCell ref="A25:S25"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="A16:S16"/>
-    <mergeCell ref="A18:S18"/>
-    <mergeCell ref="A19:S19"/>
-    <mergeCell ref="A20:S20"/>
-    <mergeCell ref="P17:S17"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="K5:S5"/>
-    <mergeCell ref="A13:S13"/>
-    <mergeCell ref="A14:S14"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:S3"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -6456,36 +6123,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="86" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="87"/>
-      <c r="N1" s="87"/>
-      <c r="O1" s="87"/>
-      <c r="P1" s="87"/>
-      <c r="Q1" s="87"/>
-      <c r="R1" s="87"/>
-      <c r="S1" s="87"/>
-      <c r="T1" s="87"/>
-      <c r="U1" s="87"/>
-      <c r="V1" s="87"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="87"/>
-      <c r="Y1" s="87"/>
-      <c r="Z1" s="87"/>
-      <c r="AA1" s="87"/>
-      <c r="AB1" s="87"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
+      <c r="N1" s="86"/>
+      <c r="O1" s="86"/>
+      <c r="P1" s="86"/>
+      <c r="Q1" s="86"/>
+      <c r="R1" s="86"/>
+      <c r="S1" s="86"/>
+      <c r="T1" s="86"/>
+      <c r="U1" s="86"/>
+      <c r="V1" s="86"/>
+      <c r="W1" s="86"/>
+      <c r="X1" s="86"/>
+      <c r="Y1" s="86"/>
+      <c r="Z1" s="86"/>
+      <c r="AA1" s="86"/>
+      <c r="AB1" s="86"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" s="88"/>
@@ -6604,15 +6271,15 @@
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="86" t="s">
+      <c r="A4" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
       <c r="H4" s="17"/>
       <c r="I4" s="16"/>
       <c r="J4" s="16"/>
@@ -6636,15 +6303,15 @@
       <c r="AB4" s="16"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" s="86"/>
-      <c r="B5" s="86" t="s">
+      <c r="A5" s="87"/>
+      <c r="B5" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
       <c r="H5" s="17"/>
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
@@ -6668,15 +6335,15 @@
       <c r="AB5" s="16"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A6" s="86"/>
-      <c r="B6" s="86"/>
-      <c r="C6" s="86" t="s">
+      <c r="A6" s="87"/>
+      <c r="B6" s="87"/>
+      <c r="C6" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="87"/>
       <c r="H6" s="17"/>
       <c r="I6" s="16"/>
       <c r="J6" s="16"/>
@@ -6700,15 +6367,15 @@
       <c r="AB6" s="16"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A7" s="86"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86" t="s">
+      <c r="A7" s="87"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
       <c r="H7" s="17"/>
       <c r="I7" s="16"/>
       <c r="J7" s="16"/>
@@ -6732,15 +6399,15 @@
       <c r="AB7" s="16"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A8" s="86"/>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86" t="s">
+      <c r="A8" s="87"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
       <c r="H8" s="17"/>
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
@@ -6764,10 +6431,10 @@
       <c r="AB8" s="16"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A9" s="86"/>
-      <c r="B9" s="86"/>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
+      <c r="A9" s="87"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
@@ -6794,10 +6461,10 @@
       <c r="AB9" s="16"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A10" s="86"/>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
+      <c r="A10" s="87"/>
+      <c r="B10" s="87"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="87"/>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="G10" s="16"/>
@@ -6824,10 +6491,10 @@
       <c r="AB10" s="16"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A11" s="86"/>
-      <c r="B11" s="86"/>
-      <c r="C11" s="86"/>
-      <c r="D11" s="86"/>
+      <c r="A11" s="87"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="87"/>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
@@ -6854,10 +6521,10 @@
       <c r="AB11" s="16"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A12" s="86"/>
-      <c r="B12" s="86"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86"/>
+      <c r="A12" s="87"/>
+      <c r="B12" s="87"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87"/>
       <c r="E12" s="16"/>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
@@ -6884,10 +6551,10 @@
       <c r="AB12" s="16"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A13" s="86"/>
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
-      <c r="D13" s="86"/>
+      <c r="A13" s="87"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
@@ -6914,10 +6581,10 @@
       <c r="AB13" s="16"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A14" s="86"/>
-      <c r="B14" s="86"/>
-      <c r="C14" s="86"/>
-      <c r="D14" s="86"/>
+      <c r="A14" s="87"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="87"/>
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
@@ -6944,10 +6611,10 @@
       <c r="AB14" s="16"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A15" s="86"/>
-      <c r="B15" s="86"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="86"/>
+      <c r="A15" s="87"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="87"/>
       <c r="E15" s="16"/>
       <c r="F15" s="16"/>
       <c r="G15" s="16"/>
@@ -6974,10 +6641,10 @@
       <c r="AB15" s="16"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A16" s="86"/>
-      <c r="B16" s="86"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
+      <c r="A16" s="87"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
       <c r="E16" s="16"/>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
@@ -7004,10 +6671,10 @@
       <c r="AB16" s="16"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A17" s="86"/>
-      <c r="B17" s="86"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
+      <c r="A17" s="87"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
       <c r="E17" s="16"/>
       <c r="F17" s="16"/>
       <c r="G17" s="16"/>
@@ -7034,10 +6701,10 @@
       <c r="AB17" s="16"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A18" s="86"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
+      <c r="A18" s="87"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="87"/>
       <c r="E18" s="16"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
@@ -7064,10 +6731,10 @@
       <c r="AB18" s="16"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A19" s="86"/>
-      <c r="B19" s="86"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
+      <c r="A19" s="87"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
@@ -7094,10 +6761,10 @@
       <c r="AB19" s="16"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A20" s="86"/>
-      <c r="B20" s="86"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
+      <c r="A20" s="87"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
       <c r="E20" s="16"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
@@ -7124,10 +6791,10 @@
       <c r="AB20" s="16"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A21" s="86"/>
-      <c r="B21" s="86"/>
-      <c r="C21" s="86"/>
-      <c r="D21" s="86"/>
+      <c r="A21" s="87"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
       <c r="E21" s="16"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
@@ -7154,10 +6821,10 @@
       <c r="AB21" s="16"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
+      <c r="A22" s="87"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
       <c r="E22" s="16"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
@@ -7184,10 +6851,10 @@
       <c r="AB22" s="16"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A23" s="86"/>
-      <c r="B23" s="86"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="86"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="87"/>
       <c r="E23" s="16"/>
       <c r="F23" s="16"/>
       <c r="G23" s="16"/>
@@ -7214,10 +6881,10 @@
       <c r="AB23" s="16"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A24" s="86"/>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86"/>
-      <c r="D24" s="86"/>
+      <c r="A24" s="87"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="87"/>
+      <c r="D24" s="87"/>
       <c r="E24" s="16"/>
       <c r="F24" s="16"/>
       <c r="G24" s="16"/>
@@ -7245,17 +6912,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="A5:A24"/>
+    <mergeCell ref="B6:B24"/>
+    <mergeCell ref="C7:C24"/>
+    <mergeCell ref="D8:D24"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="A2:AB2"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="A5:A24"/>
-    <mergeCell ref="B6:B24"/>
-    <mergeCell ref="C7:C24"/>
-    <mergeCell ref="D8:D24"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -7285,38 +6952,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="86" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="87"/>
-      <c r="N1" s="87"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
+      <c r="N1" s="86"/>
     </row>
     <row r="2" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="87"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="87"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
     </row>
     <row r="3" spans="1:14" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="89" t="s">
@@ -7337,42 +7004,42 @@
       <c r="N3" s="89"/>
     </row>
     <row r="4" spans="1:14" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="86" t="s">
+      <c r="A4" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="86" t="s">
+      <c r="D4" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="86" t="s">
+      <c r="E4" s="87" t="s">
         <v>102</v>
       </c>
-      <c r="F4" s="86" t="s">
+      <c r="F4" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="86" t="s">
+      <c r="G4" s="87" t="s">
         <v>103</v>
       </c>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="86"/>
-      <c r="N4" s="86"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
+      <c r="N4" s="87"/>
     </row>
     <row r="5" spans="1:14" ht="30.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="86"/>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
+      <c r="A5" s="87"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
       <c r="G5" s="16" t="s">
         <v>67</v>
       </c>
@@ -7399,15 +7066,15 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
       <c r="F6" s="16" t="s">
         <v>110</v>
       </c>
@@ -7421,11 +7088,11 @@
       <c r="N6" s="17"/>
     </row>
     <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="86"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
+      <c r="A7" s="87"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
       <c r="F7" s="16" t="s">
         <v>68</v>
       </c>
@@ -7439,11 +7106,11 @@
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="86"/>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
+      <c r="A8" s="87"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
       <c r="F8" s="16" t="s">
         <v>69</v>
       </c>
@@ -7457,13 +7124,13 @@
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="86"/>
-      <c r="B9" s="86"/>
-      <c r="C9" s="86" t="s">
+      <c r="A9" s="87"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
       <c r="F9" s="16" t="s">
         <v>110</v>
       </c>
@@ -7477,11 +7144,11 @@
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="86"/>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
+      <c r="A10" s="87"/>
+      <c r="B10" s="87"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
       <c r="F10" s="16" t="s">
         <v>68</v>
       </c>
@@ -7495,11 +7162,11 @@
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="86"/>
-      <c r="B11" s="86"/>
-      <c r="C11" s="86"/>
-      <c r="D11" s="86"/>
-      <c r="E11" s="86"/>
+      <c r="A11" s="87"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
       <c r="F11" s="16" t="s">
         <v>69</v>
       </c>
@@ -7513,13 +7180,13 @@
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="86"/>
-      <c r="B12" s="86"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86" t="s">
+      <c r="A12" s="87"/>
+      <c r="B12" s="87"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="E12" s="86"/>
+      <c r="E12" s="87"/>
       <c r="F12" s="16" t="s">
         <v>110</v>
       </c>
@@ -7533,11 +7200,11 @@
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="86"/>
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="86"/>
+      <c r="A13" s="87"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
       <c r="F13" s="16" t="s">
         <v>68</v>
       </c>
@@ -7551,11 +7218,11 @@
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="86"/>
-      <c r="B14" s="86"/>
-      <c r="C14" s="86"/>
-      <c r="D14" s="86"/>
-      <c r="E14" s="86"/>
+      <c r="A14" s="87"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
       <c r="F14" s="16" t="s">
         <v>69</v>
       </c>
@@ -7569,11 +7236,11 @@
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="86"/>
-      <c r="B15" s="86"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="86"/>
-      <c r="E15" s="86" t="s">
+      <c r="A15" s="87"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="87" t="s">
         <v>110</v>
       </c>
       <c r="F15" s="16" t="s">
@@ -7589,11 +7256,11 @@
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="86"/>
-      <c r="B16" s="86"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
+      <c r="A16" s="87"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
       <c r="F16" s="16" t="s">
         <v>68</v>
       </c>
@@ -7607,11 +7274,11 @@
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="86"/>
-      <c r="B17" s="86"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86"/>
+      <c r="A17" s="87"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
       <c r="F17" s="16" t="s">
         <v>69</v>
       </c>
@@ -7625,11 +7292,11 @@
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="86"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
+      <c r="A18" s="87"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
       <c r="F18" s="16" t="s">
         <v>110</v>
       </c>
@@ -7643,11 +7310,11 @@
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="86"/>
-      <c r="B19" s="86"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86"/>
+      <c r="A19" s="87"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
       <c r="F19" s="16" t="s">
         <v>68</v>
       </c>
@@ -7661,11 +7328,11 @@
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="86"/>
-      <c r="B20" s="86"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86"/>
+      <c r="A20" s="87"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
       <c r="F20" s="16" t="s">
         <v>69</v>
       </c>
@@ -7679,15 +7346,15 @@
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="86" t="s">
+      <c r="A21" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="86" t="s">
+      <c r="B21" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="86"/>
-      <c r="D21" s="86"/>
-      <c r="E21" s="86"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
       <c r="F21" s="16" t="s">
         <v>110</v>
       </c>
@@ -7701,11 +7368,11 @@
       <c r="N21" s="18"/>
     </row>
     <row r="22" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
+      <c r="A22" s="87"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="87"/>
       <c r="F22" s="16" t="s">
         <v>68</v>
       </c>
@@ -7719,11 +7386,11 @@
       <c r="N22" s="18"/>
     </row>
     <row r="23" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="86"/>
-      <c r="B23" s="86"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="86"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="87"/>
+      <c r="E23" s="87"/>
       <c r="F23" s="16" t="s">
         <v>69</v>
       </c>
@@ -7737,13 +7404,13 @@
       <c r="N23" s="18"/>
     </row>
     <row r="24" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="86"/>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86" t="s">
+      <c r="A24" s="87"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="86"/>
-      <c r="E24" s="86"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
       <c r="F24" s="16" t="s">
         <v>110</v>
       </c>
@@ -7757,11 +7424,11 @@
       <c r="N24" s="18"/>
     </row>
     <row r="25" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="86"/>
-      <c r="B25" s="86"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="87"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
       <c r="F25" s="16" t="s">
         <v>68</v>
       </c>
@@ -7775,11 +7442,11 @@
       <c r="N25" s="18"/>
     </row>
     <row r="26" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="86"/>
-      <c r="B26" s="86"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
+      <c r="A26" s="87"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
       <c r="F26" s="16" t="s">
         <v>69</v>
       </c>
@@ -7793,13 +7460,13 @@
       <c r="N26" s="18"/>
     </row>
     <row r="27" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="86"/>
-      <c r="B27" s="86"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="86" t="s">
+      <c r="A27" s="87"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="E27" s="86"/>
+      <c r="E27" s="87"/>
       <c r="F27" s="16" t="s">
         <v>110</v>
       </c>
@@ -7813,11 +7480,11 @@
       <c r="N27" s="18"/>
     </row>
     <row r="28" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="86"/>
-      <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
+      <c r="A28" s="87"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="87"/>
+      <c r="E28" s="87"/>
       <c r="F28" s="16" t="s">
         <v>68</v>
       </c>
@@ -7831,11 +7498,11 @@
       <c r="N28" s="18"/>
     </row>
     <row r="29" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="86"/>
-      <c r="B29" s="86"/>
-      <c r="C29" s="86"/>
-      <c r="D29" s="86"/>
-      <c r="E29" s="86"/>
+      <c r="A29" s="87"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="87"/>
       <c r="F29" s="16" t="s">
         <v>69</v>
       </c>
@@ -7849,11 +7516,11 @@
       <c r="N29" s="18"/>
     </row>
     <row r="30" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="86"/>
-      <c r="B30" s="86"/>
-      <c r="C30" s="86"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="86" t="s">
+      <c r="A30" s="87"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="87" t="s">
         <v>110</v>
       </c>
       <c r="F30" s="16" t="s">
@@ -7869,11 +7536,11 @@
       <c r="N30" s="18"/>
     </row>
     <row r="31" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="86"/>
-      <c r="B31" s="86"/>
-      <c r="C31" s="86"/>
-      <c r="D31" s="86"/>
-      <c r="E31" s="86"/>
+      <c r="A31" s="87"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="87"/>
       <c r="F31" s="16" t="s">
         <v>68</v>
       </c>
@@ -7887,11 +7554,11 @@
       <c r="N31" s="18"/>
     </row>
     <row r="32" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="86"/>
-      <c r="B32" s="86"/>
-      <c r="C32" s="86"/>
-      <c r="D32" s="86"/>
-      <c r="E32" s="86"/>
+      <c r="A32" s="87"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87"/>
       <c r="F32" s="16" t="s">
         <v>69</v>
       </c>
@@ -7905,11 +7572,11 @@
       <c r="N32" s="18"/>
     </row>
     <row r="33" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="86"/>
-      <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
+      <c r="A33" s="87"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="87"/>
       <c r="F33" s="16" t="s">
         <v>110</v>
       </c>
@@ -7923,11 +7590,11 @@
       <c r="N33" s="18"/>
     </row>
     <row r="34" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="86"/>
-      <c r="B34" s="86"/>
-      <c r="C34" s="86"/>
-      <c r="D34" s="86"/>
-      <c r="E34" s="86"/>
+      <c r="A34" s="87"/>
+      <c r="B34" s="87"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="87"/>
+      <c r="E34" s="87"/>
       <c r="F34" s="16" t="s">
         <v>68</v>
       </c>
@@ -7941,11 +7608,11 @@
       <c r="N34" s="18"/>
     </row>
     <row r="35" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="86"/>
-      <c r="B35" s="86"/>
-      <c r="C35" s="86"/>
-      <c r="D35" s="86"/>
-      <c r="E35" s="86"/>
+      <c r="A35" s="87"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="87"/>
+      <c r="D35" s="87"/>
+      <c r="E35" s="87"/>
       <c r="F35" s="16" t="s">
         <v>69</v>
       </c>
@@ -7960,6 +7627,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="A1:N2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:N4"/>
+    <mergeCell ref="A6:A20"/>
+    <mergeCell ref="A3:N3"/>
     <mergeCell ref="A21:A35"/>
     <mergeCell ref="B6:E8"/>
     <mergeCell ref="C9:E11"/>
@@ -7976,17 +7654,6 @@
     <mergeCell ref="D30:D35"/>
     <mergeCell ref="E33:E35"/>
     <mergeCell ref="D15:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="A1:N2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:N4"/>
-    <mergeCell ref="A6:A20"/>
-    <mergeCell ref="A3:N3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -8014,44 +7681,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="86" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="87"/>
-      <c r="N1" s="87"/>
-      <c r="O1" s="87"/>
-      <c r="P1" s="87"/>
-      <c r="Q1" s="87"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
+      <c r="N1" s="86"/>
+      <c r="O1" s="86"/>
+      <c r="P1" s="86"/>
+      <c r="Q1" s="86"/>
     </row>
     <row r="2" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="87"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="87"/>
-      <c r="P2" s="87"/>
-      <c r="Q2" s="87"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="86"/>
+      <c r="Q2" s="86"/>
     </row>
     <row r="3" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="89" t="s">
@@ -8075,45 +7742,45 @@
       <c r="Q3" s="89"/>
     </row>
     <row r="4" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="86" t="s">
+      <c r="A4" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="86" t="s">
+      <c r="D4" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="86" t="s">
+      <c r="E4" s="87" t="s">
         <v>102</v>
       </c>
-      <c r="F4" s="86" t="s">
+      <c r="F4" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="86" t="s">
+      <c r="G4" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="86"/>
-      <c r="N4" s="86"/>
-      <c r="O4" s="86"/>
-      <c r="P4" s="86"/>
-      <c r="Q4" s="86"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
+      <c r="N4" s="87"/>
+      <c r="O4" s="87"/>
+      <c r="P4" s="87"/>
+      <c r="Q4" s="87"/>
     </row>
     <row r="5" spans="1:17" ht="30.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="86"/>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
+      <c r="A5" s="87"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
       <c r="G5" s="16" t="s">
         <v>67</v>
       </c>
@@ -8149,15 +7816,15 @@
       </c>
     </row>
     <row r="6" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
       <c r="F6" s="16" t="s">
         <v>110</v>
       </c>
@@ -8174,11 +7841,11 @@
       <c r="Q6" s="17"/>
     </row>
     <row r="7" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="86"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
+      <c r="A7" s="87"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
       <c r="F7" s="16" t="s">
         <v>68</v>
       </c>
@@ -8195,11 +7862,11 @@
       <c r="Q7" s="17"/>
     </row>
     <row r="8" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="86"/>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
+      <c r="A8" s="87"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
       <c r="F8" s="16" t="s">
         <v>69</v>
       </c>
@@ -8216,13 +7883,13 @@
       <c r="Q8" s="17"/>
     </row>
     <row r="9" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="86"/>
-      <c r="B9" s="86"/>
-      <c r="C9" s="86" t="s">
+      <c r="A9" s="87"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
       <c r="F9" s="16" t="s">
         <v>110</v>
       </c>
@@ -8239,11 +7906,11 @@
       <c r="Q9" s="17"/>
     </row>
     <row r="10" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="86"/>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
+      <c r="A10" s="87"/>
+      <c r="B10" s="87"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
       <c r="F10" s="16" t="s">
         <v>68</v>
       </c>
@@ -8260,11 +7927,11 @@
       <c r="Q10" s="17"/>
     </row>
     <row r="11" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="86"/>
-      <c r="B11" s="86"/>
-      <c r="C11" s="86"/>
-      <c r="D11" s="86"/>
-      <c r="E11" s="86"/>
+      <c r="A11" s="87"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
       <c r="F11" s="16" t="s">
         <v>69</v>
       </c>
@@ -8281,13 +7948,13 @@
       <c r="Q11" s="17"/>
     </row>
     <row r="12" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="86"/>
-      <c r="B12" s="86"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86" t="s">
+      <c r="A12" s="87"/>
+      <c r="B12" s="87"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="E12" s="86"/>
+      <c r="E12" s="87"/>
       <c r="F12" s="16" t="s">
         <v>110</v>
       </c>
@@ -8304,11 +7971,11 @@
       <c r="Q12" s="17"/>
     </row>
     <row r="13" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="86"/>
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="86"/>
+      <c r="A13" s="87"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
       <c r="F13" s="16" t="s">
         <v>68</v>
       </c>
@@ -8325,11 +7992,11 @@
       <c r="Q13" s="17"/>
     </row>
     <row r="14" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="86"/>
-      <c r="B14" s="86"/>
-      <c r="C14" s="86"/>
-      <c r="D14" s="86"/>
-      <c r="E14" s="86"/>
+      <c r="A14" s="87"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
       <c r="F14" s="16" t="s">
         <v>69</v>
       </c>
@@ -8346,11 +8013,11 @@
       <c r="Q14" s="17"/>
     </row>
     <row r="15" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="86"/>
-      <c r="B15" s="86"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="86"/>
-      <c r="E15" s="86" t="s">
+      <c r="A15" s="87"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="87" t="s">
         <v>110</v>
       </c>
       <c r="F15" s="16" t="s">
@@ -8369,11 +8036,11 @@
       <c r="Q15" s="17"/>
     </row>
     <row r="16" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="86"/>
-      <c r="B16" s="86"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
+      <c r="A16" s="87"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
       <c r="F16" s="16" t="s">
         <v>68</v>
       </c>
@@ -8390,11 +8057,11 @@
       <c r="Q16" s="17"/>
     </row>
     <row r="17" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="86"/>
-      <c r="B17" s="86"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86"/>
+      <c r="A17" s="87"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
       <c r="F17" s="16" t="s">
         <v>69</v>
       </c>
@@ -8411,11 +8078,11 @@
       <c r="Q17" s="17"/>
     </row>
     <row r="18" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="86"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
+      <c r="A18" s="87"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
       <c r="F18" s="16" t="s">
         <v>110</v>
       </c>
@@ -8432,11 +8099,11 @@
       <c r="Q18" s="17"/>
     </row>
     <row r="19" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="86"/>
-      <c r="B19" s="86"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86"/>
+      <c r="A19" s="87"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
       <c r="F19" s="16" t="s">
         <v>68</v>
       </c>
@@ -8453,11 +8120,11 @@
       <c r="Q19" s="17"/>
     </row>
     <row r="20" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="86"/>
-      <c r="B20" s="86"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86"/>
+      <c r="A20" s="87"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
       <c r="F20" s="16" t="s">
         <v>69</v>
       </c>
@@ -8474,15 +8141,15 @@
       <c r="Q20" s="17"/>
     </row>
     <row r="21" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="86" t="s">
+      <c r="A21" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="86" t="s">
+      <c r="B21" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="86"/>
-      <c r="D21" s="86"/>
-      <c r="E21" s="86"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
       <c r="F21" s="16" t="s">
         <v>110</v>
       </c>
@@ -8499,11 +8166,11 @@
       <c r="Q21" s="18"/>
     </row>
     <row r="22" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
+      <c r="A22" s="87"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="87"/>
       <c r="F22" s="16" t="s">
         <v>68</v>
       </c>
@@ -8520,11 +8187,11 @@
       <c r="Q22" s="18"/>
     </row>
     <row r="23" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="86"/>
-      <c r="B23" s="86"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="86"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="87"/>
+      <c r="E23" s="87"/>
       <c r="F23" s="16" t="s">
         <v>69</v>
       </c>
@@ -8541,13 +8208,13 @@
       <c r="Q23" s="18"/>
     </row>
     <row r="24" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="86"/>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86" t="s">
+      <c r="A24" s="87"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="86"/>
-      <c r="E24" s="86"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
       <c r="F24" s="16" t="s">
         <v>110</v>
       </c>
@@ -8564,11 +8231,11 @@
       <c r="Q24" s="18"/>
     </row>
     <row r="25" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="86"/>
-      <c r="B25" s="86"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="87"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
       <c r="F25" s="16" t="s">
         <v>68</v>
       </c>
@@ -8585,11 +8252,11 @@
       <c r="Q25" s="18"/>
     </row>
     <row r="26" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="86"/>
-      <c r="B26" s="86"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
+      <c r="A26" s="87"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
       <c r="F26" s="16" t="s">
         <v>69</v>
       </c>
@@ -8606,13 +8273,13 @@
       <c r="Q26" s="18"/>
     </row>
     <row r="27" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="86"/>
-      <c r="B27" s="86"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="86" t="s">
+      <c r="A27" s="87"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="E27" s="86"/>
+      <c r="E27" s="87"/>
       <c r="F27" s="16" t="s">
         <v>110</v>
       </c>
@@ -8629,11 +8296,11 @@
       <c r="Q27" s="18"/>
     </row>
     <row r="28" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="86"/>
-      <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
+      <c r="A28" s="87"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="87"/>
+      <c r="E28" s="87"/>
       <c r="F28" s="16" t="s">
         <v>68</v>
       </c>
@@ -8650,11 +8317,11 @@
       <c r="Q28" s="18"/>
     </row>
     <row r="29" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="86"/>
-      <c r="B29" s="86"/>
-      <c r="C29" s="86"/>
-      <c r="D29" s="86"/>
-      <c r="E29" s="86"/>
+      <c r="A29" s="87"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="87"/>
       <c r="F29" s="16" t="s">
         <v>69</v>
       </c>
@@ -8671,11 +8338,11 @@
       <c r="Q29" s="18"/>
     </row>
     <row r="30" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="86"/>
-      <c r="B30" s="86"/>
-      <c r="C30" s="86"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="86" t="s">
+      <c r="A30" s="87"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="87" t="s">
         <v>110</v>
       </c>
       <c r="F30" s="16" t="s">
@@ -8694,11 +8361,11 @@
       <c r="Q30" s="18"/>
     </row>
     <row r="31" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="86"/>
-      <c r="B31" s="86"/>
-      <c r="C31" s="86"/>
-      <c r="D31" s="86"/>
-      <c r="E31" s="86"/>
+      <c r="A31" s="87"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="87"/>
       <c r="F31" s="16" t="s">
         <v>68</v>
       </c>
@@ -8715,11 +8382,11 @@
       <c r="Q31" s="18"/>
     </row>
     <row r="32" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="86"/>
-      <c r="B32" s="86"/>
-      <c r="C32" s="86"/>
-      <c r="D32" s="86"/>
-      <c r="E32" s="86"/>
+      <c r="A32" s="87"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87"/>
       <c r="F32" s="16" t="s">
         <v>69</v>
       </c>
@@ -8736,11 +8403,11 @@
       <c r="Q32" s="18"/>
     </row>
     <row r="33" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="86"/>
-      <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
+      <c r="A33" s="87"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="87"/>
       <c r="F33" s="16" t="s">
         <v>110</v>
       </c>
@@ -8757,11 +8424,11 @@
       <c r="Q33" s="18"/>
     </row>
     <row r="34" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="86"/>
-      <c r="B34" s="86"/>
-      <c r="C34" s="86"/>
-      <c r="D34" s="86"/>
-      <c r="E34" s="86"/>
+      <c r="A34" s="87"/>
+      <c r="B34" s="87"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="87"/>
+      <c r="E34" s="87"/>
       <c r="F34" s="16" t="s">
         <v>68</v>
       </c>
@@ -8778,11 +8445,11 @@
       <c r="Q34" s="18"/>
     </row>
     <row r="35" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="86"/>
-      <c r="B35" s="86"/>
-      <c r="C35" s="86"/>
-      <c r="D35" s="86"/>
-      <c r="E35" s="86"/>
+      <c r="A35" s="87"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="87"/>
+      <c r="D35" s="87"/>
+      <c r="E35" s="87"/>
       <c r="F35" s="16" t="s">
         <v>69</v>
       </c>
@@ -8800,6 +8467,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="A1:Q2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:Q4"/>
+    <mergeCell ref="A6:A20"/>
+    <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A21:A35"/>
     <mergeCell ref="B6:E8"/>
     <mergeCell ref="C9:E11"/>
@@ -8816,22 +8494,11 @@
     <mergeCell ref="D30:D35"/>
     <mergeCell ref="E33:E35"/>
     <mergeCell ref="D15:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="A1:Q2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:Q4"/>
-    <mergeCell ref="A6:A20"/>
-    <mergeCell ref="A3:Q3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157477" right="0.39370078740157477" top="0.4724409448818897" bottom="0.4724409448818897" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" fitToHeight="0" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="89" fitToHeight="0" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8858,44 +8525,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="86" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="87"/>
-      <c r="N1" s="87"/>
-      <c r="O1" s="87"/>
-      <c r="P1" s="87"/>
-      <c r="Q1" s="87"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
+      <c r="N1" s="86"/>
+      <c r="O1" s="86"/>
+      <c r="P1" s="86"/>
+      <c r="Q1" s="86"/>
     </row>
     <row r="2" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="87"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="87"/>
-      <c r="P2" s="87"/>
-      <c r="Q2" s="87"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="86"/>
+      <c r="Q2" s="86"/>
     </row>
     <row r="3" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="89" t="s">
@@ -8919,105 +8586,105 @@
       <c r="Q3" s="89"/>
     </row>
     <row r="4" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="86" t="s">
+      <c r="A4" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="86" t="s">
+      <c r="D4" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="86" t="s">
+      <c r="E4" s="87" t="s">
         <v>102</v>
       </c>
-      <c r="F4" s="86" t="s">
+      <c r="F4" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="86" t="s">
+      <c r="G4" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="86"/>
-      <c r="N4" s="86"/>
-      <c r="O4" s="86"/>
-      <c r="P4" s="86"/>
-      <c r="Q4" s="86"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
+      <c r="N4" s="87"/>
+      <c r="O4" s="87"/>
+      <c r="P4" s="87"/>
+      <c r="Q4" s="87"/>
     </row>
     <row r="5" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="86"/>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86" t="s">
+      <c r="A5" s="87"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="86" t="s">
+      <c r="H5" s="87" t="s">
         <v>117</v>
       </c>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="86"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="86"/>
-      <c r="N5" s="86"/>
-      <c r="O5" s="86" t="s">
+      <c r="I5" s="87"/>
+      <c r="J5" s="87"/>
+      <c r="K5" s="87"/>
+      <c r="L5" s="87"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="P5" s="86"/>
-      <c r="Q5" s="86"/>
+      <c r="P5" s="87"/>
+      <c r="Q5" s="87"/>
     </row>
     <row r="6" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="86"/>
-      <c r="B6" s="86"/>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86" t="s">
+      <c r="A6" s="87"/>
+      <c r="B6" s="87"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="87"/>
+      <c r="H6" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="I6" s="86" t="s">
+      <c r="I6" s="87" t="s">
         <v>119</v>
       </c>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="86" t="s">
+      <c r="J6" s="87"/>
+      <c r="K6" s="87"/>
+      <c r="L6" s="87"/>
+      <c r="M6" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="N6" s="86" t="s">
+      <c r="N6" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="O6" s="86" t="s">
+      <c r="O6" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="P6" s="86" t="s">
+      <c r="P6" s="87" t="s">
         <v>122</v>
       </c>
-      <c r="Q6" s="86" t="s">
+      <c r="Q6" s="87" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="86"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
+      <c r="A7" s="87"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
       <c r="I7" s="16" t="s">
         <v>110</v>
       </c>
@@ -9030,22 +8697,22 @@
       <c r="L7" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="M7" s="86"/>
-      <c r="N7" s="86"/>
-      <c r="O7" s="86"/>
-      <c r="P7" s="86"/>
-      <c r="Q7" s="86"/>
+      <c r="M7" s="87"/>
+      <c r="N7" s="87"/>
+      <c r="O7" s="87"/>
+      <c r="P7" s="87"/>
+      <c r="Q7" s="87"/>
     </row>
     <row r="8" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
       <c r="F8" s="16" t="s">
         <v>110</v>
       </c>
@@ -9062,11 +8729,11 @@
       <c r="Q8" s="17"/>
     </row>
     <row r="9" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="86"/>
-      <c r="B9" s="86"/>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
+      <c r="A9" s="87"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
       <c r="F9" s="16" t="s">
         <v>68</v>
       </c>
@@ -9083,11 +8750,11 @@
       <c r="Q9" s="17"/>
     </row>
     <row r="10" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="86"/>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
+      <c r="A10" s="87"/>
+      <c r="B10" s="87"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
       <c r="F10" s="16" t="s">
         <v>69</v>
       </c>
@@ -9104,13 +8771,13 @@
       <c r="Q10" s="17"/>
     </row>
     <row r="11" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="86"/>
-      <c r="B11" s="86"/>
-      <c r="C11" s="86" t="s">
+      <c r="A11" s="87"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="86"/>
-      <c r="E11" s="86"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
       <c r="F11" s="16" t="s">
         <v>110</v>
       </c>
@@ -9127,11 +8794,11 @@
       <c r="Q11" s="17"/>
     </row>
     <row r="12" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="86"/>
-      <c r="B12" s="86"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86"/>
-      <c r="E12" s="86"/>
+      <c r="A12" s="87"/>
+      <c r="B12" s="87"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
       <c r="F12" s="16" t="s">
         <v>68</v>
       </c>
@@ -9148,11 +8815,11 @@
       <c r="Q12" s="17"/>
     </row>
     <row r="13" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="86"/>
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="86"/>
+      <c r="A13" s="87"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
       <c r="F13" s="16" t="s">
         <v>69</v>
       </c>
@@ -9169,13 +8836,13 @@
       <c r="Q13" s="17"/>
     </row>
     <row r="14" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="86"/>
-      <c r="B14" s="86"/>
-      <c r="C14" s="86"/>
-      <c r="D14" s="86" t="s">
+      <c r="A14" s="87"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="E14" s="86"/>
+      <c r="E14" s="87"/>
       <c r="F14" s="16" t="s">
         <v>110</v>
       </c>
@@ -9192,11 +8859,11 @@
       <c r="Q14" s="17"/>
     </row>
     <row r="15" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="86"/>
-      <c r="B15" s="86"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="86"/>
-      <c r="E15" s="86"/>
+      <c r="A15" s="87"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="87"/>
       <c r="F15" s="16" t="s">
         <v>68</v>
       </c>
@@ -9213,11 +8880,11 @@
       <c r="Q15" s="17"/>
     </row>
     <row r="16" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="86"/>
-      <c r="B16" s="86"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
+      <c r="A16" s="87"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
       <c r="F16" s="16" t="s">
         <v>69</v>
       </c>
@@ -9234,11 +8901,11 @@
       <c r="Q16" s="17"/>
     </row>
     <row r="17" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="86"/>
-      <c r="B17" s="86"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86" t="s">
+      <c r="A17" s="87"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87" t="s">
         <v>110</v>
       </c>
       <c r="F17" s="16" t="s">
@@ -9257,11 +8924,11 @@
       <c r="Q17" s="17"/>
     </row>
     <row r="18" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="86"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
+      <c r="A18" s="87"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
       <c r="F18" s="16" t="s">
         <v>68</v>
       </c>
@@ -9278,11 +8945,11 @@
       <c r="Q18" s="17"/>
     </row>
     <row r="19" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="86"/>
-      <c r="B19" s="86"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86"/>
+      <c r="A19" s="87"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
       <c r="F19" s="16" t="s">
         <v>69</v>
       </c>
@@ -9299,11 +8966,11 @@
       <c r="Q19" s="17"/>
     </row>
     <row r="20" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="86"/>
-      <c r="B20" s="86"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86"/>
+      <c r="A20" s="87"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
       <c r="F20" s="16" t="s">
         <v>110</v>
       </c>
@@ -9320,11 +8987,11 @@
       <c r="Q20" s="17"/>
     </row>
     <row r="21" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="86"/>
-      <c r="B21" s="86"/>
-      <c r="C21" s="86"/>
-      <c r="D21" s="86"/>
-      <c r="E21" s="86"/>
+      <c r="A21" s="87"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
       <c r="F21" s="16" t="s">
         <v>68</v>
       </c>
@@ -9341,11 +9008,11 @@
       <c r="Q21" s="17"/>
     </row>
     <row r="22" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
+      <c r="A22" s="87"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="87"/>
       <c r="F22" s="16" t="s">
         <v>69</v>
       </c>
@@ -9362,15 +9029,15 @@
       <c r="Q22" s="17"/>
     </row>
     <row r="23" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="86" t="s">
+      <c r="A23" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="B23" s="86" t="s">
+      <c r="B23" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="86"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="86"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="87"/>
+      <c r="E23" s="87"/>
       <c r="F23" s="16" t="s">
         <v>110</v>
       </c>
@@ -9387,11 +9054,11 @@
       <c r="Q23" s="18"/>
     </row>
     <row r="24" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="86"/>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86"/>
-      <c r="D24" s="86"/>
-      <c r="E24" s="86"/>
+      <c r="A24" s="87"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="87"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
       <c r="F24" s="16" t="s">
         <v>68</v>
       </c>
@@ -9408,11 +9075,11 @@
       <c r="Q24" s="18"/>
     </row>
     <row r="25" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="86"/>
-      <c r="B25" s="86"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="87"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
       <c r="F25" s="16" t="s">
         <v>69</v>
       </c>
@@ -9429,13 +9096,13 @@
       <c r="Q25" s="18"/>
     </row>
     <row r="26" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="86"/>
-      <c r="B26" s="86"/>
-      <c r="C26" s="86" t="s">
+      <c r="A26" s="87"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
       <c r="F26" s="16" t="s">
         <v>110</v>
       </c>
@@ -9452,11 +9119,11 @@
       <c r="Q26" s="18"/>
     </row>
     <row r="27" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="86"/>
-      <c r="B27" s="86"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="86"/>
-      <c r="E27" s="86"/>
+      <c r="A27" s="87"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="87"/>
       <c r="F27" s="16" t="s">
         <v>68</v>
       </c>
@@ -9473,11 +9140,11 @@
       <c r="Q27" s="18"/>
     </row>
     <row r="28" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="86"/>
-      <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
+      <c r="A28" s="87"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="87"/>
+      <c r="E28" s="87"/>
       <c r="F28" s="16" t="s">
         <v>69</v>
       </c>
@@ -9494,13 +9161,13 @@
       <c r="Q28" s="18"/>
     </row>
     <row r="29" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="86"/>
-      <c r="B29" s="86"/>
-      <c r="C29" s="86"/>
-      <c r="D29" s="86" t="s">
+      <c r="A29" s="87"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="E29" s="86"/>
+      <c r="E29" s="87"/>
       <c r="F29" s="16" t="s">
         <v>110</v>
       </c>
@@ -9517,11 +9184,11 @@
       <c r="Q29" s="18"/>
     </row>
     <row r="30" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="86"/>
-      <c r="B30" s="86"/>
-      <c r="C30" s="86"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="86"/>
+      <c r="A30" s="87"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="87"/>
       <c r="F30" s="16" t="s">
         <v>68</v>
       </c>
@@ -9538,11 +9205,11 @@
       <c r="Q30" s="18"/>
     </row>
     <row r="31" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="86"/>
-      <c r="B31" s="86"/>
-      <c r="C31" s="86"/>
-      <c r="D31" s="86"/>
-      <c r="E31" s="86"/>
+      <c r="A31" s="87"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="87"/>
       <c r="F31" s="16" t="s">
         <v>69</v>
       </c>
@@ -9559,11 +9226,11 @@
       <c r="Q31" s="18"/>
     </row>
     <row r="32" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="86"/>
-      <c r="B32" s="86"/>
-      <c r="C32" s="86"/>
-      <c r="D32" s="86"/>
-      <c r="E32" s="86" t="s">
+      <c r="A32" s="87"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87" t="s">
         <v>110</v>
       </c>
       <c r="F32" s="16" t="s">
@@ -9582,11 +9249,11 @@
       <c r="Q32" s="18"/>
     </row>
     <row r="33" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="86"/>
-      <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
+      <c r="A33" s="87"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="87"/>
       <c r="F33" s="16" t="s">
         <v>68</v>
       </c>
@@ -9603,11 +9270,11 @@
       <c r="Q33" s="18"/>
     </row>
     <row r="34" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="86"/>
-      <c r="B34" s="86"/>
-      <c r="C34" s="86"/>
-      <c r="D34" s="86"/>
-      <c r="E34" s="86"/>
+      <c r="A34" s="87"/>
+      <c r="B34" s="87"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="87"/>
+      <c r="E34" s="87"/>
       <c r="F34" s="16" t="s">
         <v>69</v>
       </c>
@@ -9624,11 +9291,11 @@
       <c r="Q34" s="18"/>
     </row>
     <row r="35" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="86"/>
-      <c r="B35" s="86"/>
-      <c r="C35" s="86"/>
-      <c r="D35" s="86"/>
-      <c r="E35" s="86"/>
+      <c r="A35" s="87"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="87"/>
+      <c r="D35" s="87"/>
+      <c r="E35" s="87"/>
       <c r="F35" s="16" t="s">
         <v>110</v>
       </c>
@@ -9645,11 +9312,11 @@
       <c r="Q35" s="18"/>
     </row>
     <row r="36" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="86"/>
-      <c r="B36" s="86"/>
-      <c r="C36" s="86"/>
-      <c r="D36" s="86"/>
-      <c r="E36" s="86"/>
+      <c r="A36" s="87"/>
+      <c r="B36" s="87"/>
+      <c r="C36" s="87"/>
+      <c r="D36" s="87"/>
+      <c r="E36" s="87"/>
       <c r="F36" s="16" t="s">
         <v>68</v>
       </c>
@@ -9666,11 +9333,11 @@
       <c r="Q36" s="18"/>
     </row>
     <row r="37" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="86"/>
-      <c r="B37" s="86"/>
-      <c r="C37" s="86"/>
-      <c r="D37" s="86"/>
-      <c r="E37" s="86"/>
+      <c r="A37" s="87"/>
+      <c r="B37" s="87"/>
+      <c r="C37" s="87"/>
+      <c r="D37" s="87"/>
+      <c r="E37" s="87"/>
       <c r="F37" s="16" t="s">
         <v>69</v>
       </c>
@@ -9688,6 +9355,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A1:Q2"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="G4:Q4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="D17:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="Q6:Q7"/>
     <mergeCell ref="A8:A22"/>
     <mergeCell ref="B23:E25"/>
     <mergeCell ref="C26:E28"/>
@@ -9704,32 +9392,11 @@
     <mergeCell ref="D14:E16"/>
     <mergeCell ref="C14:C22"/>
     <mergeCell ref="E17:E19"/>
-    <mergeCell ref="D17:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:P7"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="A1:Q2"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="G4:Q4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="A3:Q3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157477" right="0.39370078740157477" top="0.4724409448818897" bottom="0.4724409448818897" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="87" fitToHeight="0" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="88" fitToHeight="0" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9752,32 +9419,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="86" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
     </row>
     <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="87"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
     </row>
     <row r="3" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="89" t="s">
@@ -9795,39 +9462,39 @@
       <c r="K3" s="89"/>
     </row>
     <row r="4" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="86" t="s">
+      <c r="A4" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="86" t="s">
+      <c r="D4" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="86" t="s">
+      <c r="E4" s="87" t="s">
         <v>102</v>
       </c>
-      <c r="F4" s="86" t="s">
+      <c r="F4" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="86" t="s">
+      <c r="G4" s="87" t="s">
         <v>127</v>
       </c>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
     </row>
     <row r="5" spans="1:11" ht="30.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="86"/>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
+      <c r="A5" s="87"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
       <c r="G5" s="16" t="s">
         <v>67</v>
       </c>
@@ -9845,15 +9512,15 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
       <c r="F6" s="16" t="s">
         <v>110</v>
       </c>
@@ -9864,11 +9531,11 @@
       <c r="K6" s="17"/>
     </row>
     <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="86"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
+      <c r="A7" s="87"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
       <c r="F7" s="16" t="s">
         <v>68</v>
       </c>
@@ -9879,11 +9546,11 @@
       <c r="K7" s="17"/>
     </row>
     <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="86"/>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
+      <c r="A8" s="87"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
       <c r="F8" s="16" t="s">
         <v>69</v>
       </c>
@@ -9894,13 +9561,13 @@
       <c r="K8" s="17"/>
     </row>
     <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="86"/>
-      <c r="B9" s="86"/>
-      <c r="C9" s="86" t="s">
+      <c r="A9" s="87"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
       <c r="F9" s="16" t="s">
         <v>110</v>
       </c>
@@ -9911,11 +9578,11 @@
       <c r="K9" s="17"/>
     </row>
     <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="86"/>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
+      <c r="A10" s="87"/>
+      <c r="B10" s="87"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
       <c r="F10" s="16" t="s">
         <v>68</v>
       </c>
@@ -9926,11 +9593,11 @@
       <c r="K10" s="17"/>
     </row>
     <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="86"/>
-      <c r="B11" s="86"/>
-      <c r="C11" s="86"/>
-      <c r="D11" s="86"/>
-      <c r="E11" s="86"/>
+      <c r="A11" s="87"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
       <c r="F11" s="16" t="s">
         <v>69</v>
       </c>
@@ -9941,13 +9608,13 @@
       <c r="K11" s="17"/>
     </row>
     <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="86"/>
-      <c r="B12" s="86"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86" t="s">
+      <c r="A12" s="87"/>
+      <c r="B12" s="87"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="E12" s="86"/>
+      <c r="E12" s="87"/>
       <c r="F12" s="16" t="s">
         <v>110</v>
       </c>
@@ -9958,11 +9625,11 @@
       <c r="K12" s="17"/>
     </row>
     <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="86"/>
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="86"/>
+      <c r="A13" s="87"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
       <c r="F13" s="16" t="s">
         <v>68</v>
       </c>
@@ -9973,11 +9640,11 @@
       <c r="K13" s="17"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="86"/>
-      <c r="B14" s="86"/>
-      <c r="C14" s="86"/>
-      <c r="D14" s="86"/>
-      <c r="E14" s="86"/>
+      <c r="A14" s="87"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
       <c r="F14" s="16" t="s">
         <v>69</v>
       </c>
@@ -9988,11 +9655,11 @@
       <c r="K14" s="17"/>
     </row>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="86"/>
-      <c r="B15" s="86"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="86"/>
-      <c r="E15" s="86" t="s">
+      <c r="A15" s="87"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="87" t="s">
         <v>110</v>
       </c>
       <c r="F15" s="16" t="s">
@@ -10005,11 +9672,11 @@
       <c r="K15" s="17"/>
     </row>
     <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="86"/>
-      <c r="B16" s="86"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
+      <c r="A16" s="87"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
       <c r="F16" s="16" t="s">
         <v>68</v>
       </c>
@@ -10020,11 +9687,11 @@
       <c r="K16" s="17"/>
     </row>
     <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="86"/>
-      <c r="B17" s="86"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86"/>
+      <c r="A17" s="87"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
       <c r="F17" s="16" t="s">
         <v>69</v>
       </c>
@@ -10035,11 +9702,11 @@
       <c r="K17" s="17"/>
     </row>
     <row r="18" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="86"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
+      <c r="A18" s="87"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
       <c r="F18" s="16" t="s">
         <v>110</v>
       </c>
@@ -10050,11 +9717,11 @@
       <c r="K18" s="17"/>
     </row>
     <row r="19" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="86"/>
-      <c r="B19" s="86"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86"/>
+      <c r="A19" s="87"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
       <c r="F19" s="16" t="s">
         <v>68</v>
       </c>
@@ -10065,11 +9732,11 @@
       <c r="K19" s="17"/>
     </row>
     <row r="20" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="86"/>
-      <c r="B20" s="86"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86"/>
+      <c r="A20" s="87"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
       <c r="F20" s="16" t="s">
         <v>69</v>
       </c>
@@ -10080,15 +9747,15 @@
       <c r="K20" s="17"/>
     </row>
     <row r="21" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="86" t="s">
+      <c r="A21" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="86" t="s">
+      <c r="B21" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="86"/>
-      <c r="D21" s="86"/>
-      <c r="E21" s="86"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
       <c r="F21" s="16" t="s">
         <v>110</v>
       </c>
@@ -10099,11 +9766,11 @@
       <c r="K21" s="18"/>
     </row>
     <row r="22" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
+      <c r="A22" s="87"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="87"/>
       <c r="F22" s="16" t="s">
         <v>68</v>
       </c>
@@ -10114,11 +9781,11 @@
       <c r="K22" s="18"/>
     </row>
     <row r="23" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="86"/>
-      <c r="B23" s="86"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="86"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="87"/>
+      <c r="E23" s="87"/>
       <c r="F23" s="16" t="s">
         <v>69</v>
       </c>
@@ -10129,13 +9796,13 @@
       <c r="K23" s="18"/>
     </row>
     <row r="24" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="86"/>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86" t="s">
+      <c r="A24" s="87"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="86"/>
-      <c r="E24" s="86"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
       <c r="F24" s="16" t="s">
         <v>110</v>
       </c>
@@ -10146,11 +9813,11 @@
       <c r="K24" s="18"/>
     </row>
     <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="86"/>
-      <c r="B25" s="86"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="87"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
       <c r="F25" s="16" t="s">
         <v>68</v>
       </c>
@@ -10161,11 +9828,11 @@
       <c r="K25" s="18"/>
     </row>
     <row r="26" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="86"/>
-      <c r="B26" s="86"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
+      <c r="A26" s="87"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
       <c r="F26" s="16" t="s">
         <v>69</v>
       </c>
@@ -10176,13 +9843,13 @@
       <c r="K26" s="18"/>
     </row>
     <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="86"/>
-      <c r="B27" s="86"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="86" t="s">
+      <c r="A27" s="87"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="E27" s="86"/>
+      <c r="E27" s="87"/>
       <c r="F27" s="16" t="s">
         <v>110</v>
       </c>
@@ -10193,11 +9860,11 @@
       <c r="K27" s="18"/>
     </row>
     <row r="28" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="86"/>
-      <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
+      <c r="A28" s="87"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="87"/>
+      <c r="E28" s="87"/>
       <c r="F28" s="16" t="s">
         <v>68</v>
       </c>
@@ -10208,11 +9875,11 @@
       <c r="K28" s="18"/>
     </row>
     <row r="29" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="86"/>
-      <c r="B29" s="86"/>
-      <c r="C29" s="86"/>
-      <c r="D29" s="86"/>
-      <c r="E29" s="86"/>
+      <c r="A29" s="87"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="87"/>
       <c r="F29" s="16" t="s">
         <v>69</v>
       </c>
@@ -10223,11 +9890,11 @@
       <c r="K29" s="18"/>
     </row>
     <row r="30" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="86"/>
-      <c r="B30" s="86"/>
-      <c r="C30" s="86"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="86" t="s">
+      <c r="A30" s="87"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="87" t="s">
         <v>110</v>
       </c>
       <c r="F30" s="16" t="s">
@@ -10240,11 +9907,11 @@
       <c r="K30" s="18"/>
     </row>
     <row r="31" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="86"/>
-      <c r="B31" s="86"/>
-      <c r="C31" s="86"/>
-      <c r="D31" s="86"/>
-      <c r="E31" s="86"/>
+      <c r="A31" s="87"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="87"/>
       <c r="F31" s="16" t="s">
         <v>68</v>
       </c>
@@ -10255,11 +9922,11 @@
       <c r="K31" s="18"/>
     </row>
     <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="86"/>
-      <c r="B32" s="86"/>
-      <c r="C32" s="86"/>
-      <c r="D32" s="86"/>
-      <c r="E32" s="86"/>
+      <c r="A32" s="87"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87"/>
       <c r="F32" s="16" t="s">
         <v>69</v>
       </c>
@@ -10270,11 +9937,11 @@
       <c r="K32" s="18"/>
     </row>
     <row r="33" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="86"/>
-      <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
+      <c r="A33" s="87"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="87"/>
       <c r="F33" s="16" t="s">
         <v>110</v>
       </c>
@@ -10285,11 +9952,11 @@
       <c r="K33" s="18"/>
     </row>
     <row r="34" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="86"/>
-      <c r="B34" s="86"/>
-      <c r="C34" s="86"/>
-      <c r="D34" s="86"/>
-      <c r="E34" s="86"/>
+      <c r="A34" s="87"/>
+      <c r="B34" s="87"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="87"/>
+      <c r="E34" s="87"/>
       <c r="F34" s="16" t="s">
         <v>68</v>
       </c>
@@ -10300,11 +9967,11 @@
       <c r="K34" s="18"/>
     </row>
     <row r="35" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="86"/>
-      <c r="B35" s="86"/>
-      <c r="C35" s="86"/>
-      <c r="D35" s="86"/>
-      <c r="E35" s="86"/>
+      <c r="A35" s="87"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="87"/>
+      <c r="D35" s="87"/>
+      <c r="E35" s="87"/>
       <c r="F35" s="16" t="s">
         <v>69</v>
       </c>
@@ -10316,6 +9983,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A6:A20"/>
+    <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:A35"/>
     <mergeCell ref="B6:E8"/>
     <mergeCell ref="C9:E11"/>
@@ -10332,17 +10010,6 @@
     <mergeCell ref="D30:D35"/>
     <mergeCell ref="E33:E35"/>
     <mergeCell ref="D15:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="A1:K2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A6:A20"/>
-    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
